--- a/BOM/Client-BOM.xlsx
+++ b/BOM/Client-BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FF59C9-FF43-4DCD-985B-C4DC8910FB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C8D166-3906-4D2C-8E02-2C7A50C0213B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="364">
   <si>
     <t>Component list</t>
   </si>
@@ -1021,9 +1021,6 @@
     <t>25V 22uF X5R ±20% 0805</t>
   </si>
   <si>
-    <t>C6, C4, C36, C53</t>
-  </si>
-  <si>
     <t>Custom</t>
   </si>
   <si>
@@ -1063,9 +1060,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>C53 Not Confirm</t>
-  </si>
-  <si>
     <t xml:space="preserve">Less Stock On LCSC </t>
   </si>
   <si>
@@ -1073,6 +1067,51 @@
   </si>
   <si>
     <t>Mega2560_Custom</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>Antennas ROHS</t>
+  </si>
+  <si>
+    <t>BW4GJWX195-13KJ</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>IPEX-25x25x4.6mm Antennas ROHS</t>
+  </si>
+  <si>
+    <t>BWGNSCNX25-25B1Y2L120</t>
+  </si>
+  <si>
+    <t>65℃~+165℃ 200mm IPEX to SMA 1Gen - Radio Frequency Cable ROHS</t>
+  </si>
+  <si>
+    <t>BWIPX1-SMA-1.13L200</t>
+  </si>
+  <si>
+    <t>C6, C4, C36</t>
+  </si>
+  <si>
+    <t>C53</t>
+  </si>
+  <si>
+    <t>CAP ALUM POLY 47UF 20% 25V SMD</t>
+  </si>
+  <si>
+    <t>25SVPF47M</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>CC0402JRNPO8BN330</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1228,6 +1267,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1261,7 +1325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1469,11 +1533,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1560,19 +1637,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1597,9 +1666,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1615,6 +1681,27 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1624,25 +1711,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1986,7 +2112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2011,74 +2137,74 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="50" t="s">
-        <v>349</v>
+      <c r="F2" s="46" t="s">
+        <v>347</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="38"/>
+      <c r="L2" s="37"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="42"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="51" t="s">
-        <v>350</v>
+      <c r="F3" s="47" t="s">
+        <v>348</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="55"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="52" t="s">
-        <v>350</v>
+      <c r="F4" s="48" t="s">
+        <v>348</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="56"/>
+      <c r="L4" s="59"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="49" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="14"/>
@@ -2086,12 +2212,12 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="56"/>
+      <c r="L5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="43"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -2100,12 +2226,12 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="56"/>
+      <c r="L6" s="59"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="44"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -2114,12 +2240,12 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="56"/>
+      <c r="L7" s="59"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="45"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -2128,7 +2254,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="56"/>
+      <c r="L8" s="59"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2153,2570 +2279,2711 @@
       <c r="H9" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="I9" s="49" t="s">
-        <v>343</v>
+      <c r="I9" s="45" t="s">
+        <v>342</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="K9" s="61" t="s">
+      <c r="K9" s="54" t="s">
+        <v>344</v>
+      </c>
+      <c r="L9" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="48">
+      <c r="B10" s="65">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="76" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="76" t="s">
         <v>265</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="I10" s="76" t="s">
         <v>300</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="76">
         <v>1</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="76">
         <f>J10*5</f>
         <v>5</v>
       </c>
-      <c r="L10" s="36"/>
-    </row>
-    <row r="11" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="76"/>
+    </row>
+    <row r="11" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="48">
-        <f t="shared" ref="B11:B78" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="60">
+        <f t="shared" ref="B11:B81" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="G11" s="37" t="s">
-        <v>340</v>
-      </c>
-      <c r="H11" s="37" t="s">
+      <c r="G11" s="74" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" s="63" t="s">
         <v>265</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="63" t="s">
         <v>301</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="63">
         <v>28</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="63">
         <f t="shared" ref="K11" si="1">J11*5</f>
         <v>140</v>
       </c>
-      <c r="L11" s="37"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="63"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="48">
+      <c r="B12" s="65">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="78" t="s">
         <v>332</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="78" t="s">
         <v>167</v>
       </c>
-      <c r="G12" s="58" t="s">
+      <c r="G12" s="78" t="s">
         <v>209</v>
       </c>
-      <c r="H12" s="58" t="s">
-        <v>341</v>
-      </c>
-      <c r="I12" s="58" t="s">
+      <c r="H12" s="78" t="s">
+        <v>340</v>
+      </c>
+      <c r="I12" s="78" t="s">
         <v>302</v>
       </c>
-      <c r="J12" s="58">
+      <c r="J12" s="78">
         <v>2</v>
       </c>
-      <c r="K12" s="58">
+      <c r="K12" s="78">
         <f>J12*5</f>
         <v>10</v>
       </c>
-      <c r="L12" s="62"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="79"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="48">
+      <c r="B13" s="60">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="60" t="s">
+      <c r="D13" s="74" t="s">
+        <v>358</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="63" t="s">
         <v>333</v>
       </c>
-      <c r="E13" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="63" t="s">
         <v>266</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="63" t="s">
         <v>303</v>
       </c>
-      <c r="J13" s="37">
-        <v>4</v>
-      </c>
-      <c r="K13" s="37">
+      <c r="J13" s="63">
+        <v>3</v>
+      </c>
+      <c r="K13" s="63">
         <f t="shared" ref="K13:K14" si="2">J13*5</f>
-        <v>20</v>
-      </c>
-      <c r="L13" s="63" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L13" s="75"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="48">
-        <f>ROW(B14) - ROW($B$9)</f>
+      <c r="B14" s="60">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="78" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="78" t="s">
         <v>266</v>
       </c>
-      <c r="I14" s="58" t="s">
+      <c r="I14" s="78" t="s">
         <v>304</v>
       </c>
-      <c r="J14" s="58">
+      <c r="J14" s="78">
         <v>1</v>
       </c>
-      <c r="K14" s="58">
+      <c r="K14" s="78">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L14" s="62"/>
-    </row>
-    <row r="15" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="79"/>
+    </row>
+    <row r="15" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="48">
-        <f t="shared" si="0"/>
+      <c r="B15" s="65">
+        <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="60" t="s">
+      <c r="D15" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="63" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="63" t="s">
         <v>265</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="63" t="s">
         <v>305</v>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="63">
         <v>12</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="63">
         <f>J15*5</f>
         <v>60</v>
       </c>
-      <c r="L15" s="37"/>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="63"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="48">
-        <f>ROW(B16) - ROW($B$9)</f>
+      <c r="B16" s="60">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="78" t="s">
         <v>212</v>
       </c>
-      <c r="H16" s="58" t="s">
+      <c r="H16" s="78" t="s">
         <v>265</v>
       </c>
-      <c r="I16" s="58" t="s">
+      <c r="I16" s="78" t="s">
         <v>306</v>
       </c>
-      <c r="J16" s="58">
+      <c r="J16" s="78">
         <v>1</v>
       </c>
-      <c r="K16" s="58">
+      <c r="K16" s="78">
         <f t="shared" ref="K16" si="3">J16*5</f>
         <v>5</v>
       </c>
-      <c r="L16" s="62"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="79"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="48">
-        <f t="shared" si="0"/>
+      <c r="B17" s="65">
+        <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="60" t="s">
+      <c r="D17" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="G17" s="58" t="s">
-        <v>212</v>
-      </c>
-      <c r="H17" s="37" t="s">
+      <c r="G17" s="74" t="s">
+        <v>363</v>
+      </c>
+      <c r="H17" s="63" t="s">
         <v>267</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="63" t="s">
         <v>307</v>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="63">
         <v>1</v>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="63">
         <f>J17*5</f>
         <v>5</v>
       </c>
-      <c r="L17" s="37"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="63"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="48">
-        <f>ROW(B18) - ROW($B$9)</f>
+      <c r="B18" s="60">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" s="78" t="s">
         <v>265</v>
       </c>
-      <c r="I18" s="58" t="s">
+      <c r="I18" s="78" t="s">
         <v>308</v>
       </c>
-      <c r="J18" s="58">
+      <c r="J18" s="78">
         <v>2</v>
       </c>
-      <c r="K18" s="58">
+      <c r="K18" s="78">
         <f t="shared" ref="K18" si="4">J18*5</f>
         <v>10</v>
       </c>
-      <c r="L18" s="62"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="79"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="48">
-        <f t="shared" si="0"/>
+      <c r="B19" s="65">
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D19" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="E19" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="G19" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="63" t="s">
         <v>265</v>
       </c>
-      <c r="I19" s="37" t="s">
+      <c r="I19" s="63" t="s">
         <v>309</v>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="63">
         <v>2</v>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="63">
         <f>J19*5</f>
         <v>10</v>
       </c>
-      <c r="L19" s="37"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="63"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="48">
+      <c r="B20" s="65">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>359</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>360</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G20" s="76" t="s">
+        <v>361</v>
+      </c>
+      <c r="H20" s="76" t="s">
+        <v>266</v>
+      </c>
+      <c r="I20" s="76" t="s">
+        <v>362</v>
+      </c>
+      <c r="J20" s="76">
+        <v>1</v>
+      </c>
+      <c r="K20" s="76">
+        <f>J20*5</f>
+        <v>5</v>
+      </c>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="60">
         <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J21" s="51">
+        <v>7</v>
+      </c>
+      <c r="K21" s="51">
+        <f t="shared" ref="K21" si="5">J21*5</f>
+        <v>35</v>
+      </c>
+      <c r="L21" s="55"/>
+    </row>
+    <row r="22" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="65">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J22" s="36">
+        <v>2</v>
+      </c>
+      <c r="K22" s="36">
+        <f>J22*5</f>
+        <v>10</v>
+      </c>
+      <c r="L22" s="36"/>
+    </row>
+    <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="60">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J23" s="51">
+        <v>1</v>
+      </c>
+      <c r="K23" s="51">
+        <f t="shared" ref="K23" si="6">J23*5</f>
+        <v>5</v>
+      </c>
+      <c r="L23" s="55"/>
+    </row>
+    <row r="24" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="65">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>341</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J24" s="36">
+        <v>1</v>
+      </c>
+      <c r="K24" s="36">
+        <f>J24*5</f>
+        <v>5</v>
+      </c>
+      <c r="L24" s="36"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="60">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J25" s="51">
+        <v>8</v>
+      </c>
+      <c r="K25" s="51">
+        <f t="shared" ref="K25" si="7">J25*5</f>
+        <v>40</v>
+      </c>
+      <c r="L25" s="55"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="65">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J26" s="36">
+        <v>1</v>
+      </c>
+      <c r="K26" s="36">
+        <f>J26*5</f>
+        <v>5</v>
+      </c>
+      <c r="L26" s="36"/>
+    </row>
+    <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="60">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J27" s="51">
+        <v>3</v>
+      </c>
+      <c r="K27" s="51">
+        <f t="shared" ref="K27" si="8">J27*5</f>
+        <v>15</v>
+      </c>
+      <c r="L27" s="55"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="65">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="I28" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J28" s="36">
+        <v>1</v>
+      </c>
+      <c r="K28" s="36">
+        <f>J28*5</f>
+        <v>5</v>
+      </c>
+      <c r="L28" s="36"/>
+    </row>
+    <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="60">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="H29" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="I29" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J29" s="51">
+        <v>5</v>
+      </c>
+      <c r="K29" s="51">
+        <f t="shared" ref="K29" si="9">J29*5</f>
+        <v>25</v>
+      </c>
+      <c r="L29" s="55"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="65">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="H30" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J30" s="36">
+        <v>1</v>
+      </c>
+      <c r="K30" s="36">
+        <f>J30*5</f>
+        <v>5</v>
+      </c>
+      <c r="L30" s="36"/>
+    </row>
+    <row r="31" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="60">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="I31" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J31" s="51">
+        <v>2</v>
+      </c>
+      <c r="K31" s="51">
+        <f t="shared" ref="K31" si="10">J31*5</f>
+        <v>10</v>
+      </c>
+      <c r="L31" s="55"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="65">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="D32" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="H32" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="J32" s="36">
+        <v>1</v>
+      </c>
+      <c r="K32" s="36">
+        <f>J32*5</f>
+        <v>5</v>
+      </c>
+      <c r="L32" s="36"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="60">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J33" s="51">
         <v>8</v>
       </c>
-      <c r="D20" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G20" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H20" s="58" t="s">
-        <v>268</v>
-      </c>
-      <c r="I20" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J20" s="58">
-        <v>7</v>
-      </c>
-      <c r="K20" s="58">
-        <f t="shared" ref="K20" si="5">J20*5</f>
-        <v>35</v>
-      </c>
-      <c r="L20" s="62"/>
-    </row>
-    <row r="21" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="48">
-        <f>ROW(B21) - ROW($B$9)</f>
+      <c r="K33" s="51">
+        <f t="shared" ref="K33" si="11">J33*5</f>
+        <v>40</v>
+      </c>
+      <c r="L33" s="55"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="65">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="G21" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J21" s="37">
+      <c r="D34" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G34" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="H34" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J34" s="36">
         <v>2</v>
       </c>
-      <c r="K21" s="37">
-        <f>J21*5</f>
+      <c r="K34" s="36">
+        <f>J34*5</f>
         <v>10</v>
       </c>
-      <c r="L21" s="37"/>
-    </row>
-    <row r="22" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="48">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="F22" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="G22" s="58" t="s">
-        <v>217</v>
-      </c>
-      <c r="H22" s="58" t="s">
-        <v>270</v>
-      </c>
-      <c r="I22" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J22" s="58">
+      <c r="L34" s="36"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="60">
+        <f t="shared" ref="B35" si="12">ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="51">
+        <v>1051330011</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>229</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J35" s="51">
         <v>1</v>
       </c>
-      <c r="K22" s="58">
-        <f t="shared" ref="K22" si="6">J22*5</f>
+      <c r="K35" s="51">
+        <f t="shared" ref="K35:K36" si="13">J35*5</f>
         <v>5</v>
       </c>
-      <c r="L22" s="62"/>
-    </row>
-    <row r="23" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="48">
-        <f>ROW(B23) - ROW($B$9)</f>
-        <v>14</v>
-      </c>
-      <c r="C23" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J23" s="37">
-        <v>1</v>
-      </c>
-      <c r="K23" s="37">
-        <f>J23*5</f>
-        <v>5</v>
-      </c>
-      <c r="L23" s="37"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="48">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" s="58" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="H24" s="58" t="s">
-        <v>271</v>
-      </c>
-      <c r="I24" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J24" s="58">
-        <v>8</v>
-      </c>
-      <c r="K24" s="58">
-        <f t="shared" ref="K24" si="7">J24*5</f>
-        <v>40</v>
-      </c>
-      <c r="L24" s="62"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="48">
-        <f>ROW(B25) - ROW($B$9)</f>
-        <v>16</v>
-      </c>
-      <c r="C25" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J25" s="37">
-        <v>1</v>
-      </c>
-      <c r="K25" s="37">
-        <f>J25*5</f>
-        <v>5</v>
-      </c>
-      <c r="L25" s="37"/>
-    </row>
-    <row r="26" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="48">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="58" t="s">
-        <v>176</v>
-      </c>
-      <c r="G26" s="58" t="s">
-        <v>221</v>
-      </c>
-      <c r="H26" s="58" t="s">
-        <v>273</v>
-      </c>
-      <c r="I26" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J26" s="58">
-        <v>3</v>
-      </c>
-      <c r="K26" s="58">
-        <f t="shared" ref="K26" si="8">J26*5</f>
-        <v>15</v>
-      </c>
-      <c r="L26" s="62"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="48">
-        <f>ROW(B27) - ROW($B$9)</f>
-        <v>18</v>
-      </c>
-      <c r="C27" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J27" s="37">
-        <v>1</v>
-      </c>
-      <c r="K27" s="37">
-        <f>J27*5</f>
-        <v>5</v>
-      </c>
-      <c r="L27" s="37"/>
-    </row>
-    <row r="28" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="48">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="58" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="58" t="s">
-        <v>176</v>
-      </c>
-      <c r="G28" s="58" t="s">
-        <v>223</v>
-      </c>
-      <c r="H28" s="58" t="s">
-        <v>269</v>
-      </c>
-      <c r="I28" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J28" s="58">
-        <v>5</v>
-      </c>
-      <c r="K28" s="58">
-        <f t="shared" ref="K28" si="9">J28*5</f>
-        <v>25</v>
-      </c>
-      <c r="L28" s="62"/>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="48">
-        <f>ROW(B29) - ROW($B$9)</f>
-        <v>20</v>
-      </c>
-      <c r="C29" s="59" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J29" s="37">
-        <v>1</v>
-      </c>
-      <c r="K29" s="37">
-        <f>J29*5</f>
-        <v>5</v>
-      </c>
-      <c r="L29" s="37"/>
-    </row>
-    <row r="30" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="48">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="58" t="s">
-        <v>179</v>
-      </c>
-      <c r="G30" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="H30" s="58" t="s">
-        <v>276</v>
-      </c>
-      <c r="I30" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J30" s="58">
-        <v>2</v>
-      </c>
-      <c r="K30" s="58">
-        <f t="shared" ref="K30" si="10">J30*5</f>
-        <v>10</v>
-      </c>
-      <c r="L30" s="62"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="48">
-        <f>ROW(B31) - ROW($B$9)</f>
-        <v>22</v>
-      </c>
-      <c r="C31" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="J31" s="37">
-        <v>1</v>
-      </c>
-      <c r="K31" s="37">
-        <f>J31*5</f>
-        <v>5</v>
-      </c>
-      <c r="L31" s="37"/>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="48">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="F32" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="G32" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="H32" s="58" t="s">
-        <v>277</v>
-      </c>
-      <c r="I32" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J32" s="58">
-        <v>8</v>
-      </c>
-      <c r="K32" s="58">
-        <f t="shared" ref="K32" si="11">J32*5</f>
-        <v>40</v>
-      </c>
-      <c r="L32" s="62"/>
-    </row>
-    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="48">
-        <f>ROW(B33) - ROW($B$9)</f>
-        <v>24</v>
-      </c>
-      <c r="C33" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J33" s="37">
-        <v>2</v>
-      </c>
-      <c r="K33" s="37">
-        <f>J33*5</f>
-        <v>10</v>
-      </c>
-      <c r="L33" s="37"/>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="48">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="58">
-        <v>1051330011</v>
-      </c>
-      <c r="G34" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="H34" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="I34" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J34" s="58">
-        <v>1</v>
-      </c>
-      <c r="K34" s="58">
-        <f t="shared" ref="K34:K35" si="12">J34*5</f>
-        <v>5</v>
-      </c>
-      <c r="L34" s="62"/>
-    </row>
-    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="48">
-        <f>ROW(B35) - ROW($B$9)</f>
-        <v>26</v>
-      </c>
-      <c r="C35" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J35" s="37">
-        <v>6</v>
-      </c>
-      <c r="K35" s="37">
-        <f t="shared" si="12"/>
-        <v>30</v>
-      </c>
-      <c r="L35" s="63" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L35" s="55"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="48">
+      <c r="B36" s="60">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="I36" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="D36" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="F36" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="G36" s="58" t="s">
-        <v>230</v>
-      </c>
-      <c r="H36" s="58" t="s">
-        <v>281</v>
-      </c>
-      <c r="I36" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J36" s="58">
-        <v>2</v>
-      </c>
-      <c r="K36" s="58">
-        <f>J36*5</f>
-        <v>10</v>
-      </c>
-      <c r="L36" s="62"/>
-    </row>
-    <row r="37" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="36">
+        <v>6</v>
+      </c>
+      <c r="K36" s="36">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="L36" s="56" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="48">
+      <c r="B37" s="65">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J37" s="37">
-        <v>1</v>
-      </c>
-      <c r="K37" s="37">
-        <f t="shared" ref="K37" si="13">J37*5</f>
-        <v>5</v>
-      </c>
-      <c r="L37" s="37"/>
-    </row>
-    <row r="38" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="I37" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J37" s="51">
+        <v>2</v>
+      </c>
+      <c r="K37" s="51">
+        <f>J37*5</f>
+        <v>10</v>
+      </c>
+      <c r="L37" s="55"/>
+    </row>
+    <row r="38" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="48">
+      <c r="B38" s="60">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="F38" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="G38" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="H38" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="I38" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J38" s="58">
+      <c r="C38" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G38" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="I38" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J38" s="36">
         <v>1</v>
       </c>
-      <c r="K38" s="58">
-        <f>J38*5</f>
+      <c r="K38" s="36">
+        <f t="shared" ref="K38" si="14">J38*5</f>
         <v>5</v>
       </c>
-      <c r="L38" s="62"/>
-    </row>
-    <row r="39" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="36"/>
+    </row>
+    <row r="39" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="48">
+      <c r="B39" s="65">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="H39" s="37" t="s">
+      <c r="D39" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="I39" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J39" s="37">
+      <c r="I39" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J39" s="51">
         <v>1</v>
       </c>
-      <c r="K39" s="37">
-        <f t="shared" ref="K39" si="14">J39*5</f>
+      <c r="K39" s="51">
+        <f>J39*5</f>
         <v>5</v>
       </c>
-      <c r="L39" s="37"/>
-    </row>
-    <row r="40" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L39" s="55"/>
+    </row>
+    <row r="40" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="48">
+      <c r="B40" s="60">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E40" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="G40" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="H40" s="58" t="s">
-        <v>281</v>
-      </c>
-      <c r="I40" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J40" s="58">
+      <c r="C40" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G40" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="I40" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J40" s="36">
         <v>1</v>
       </c>
-      <c r="K40" s="58">
-        <f>J40*5</f>
+      <c r="K40" s="36">
+        <f t="shared" ref="K40" si="15">J40*5</f>
         <v>5</v>
       </c>
-      <c r="L40" s="62"/>
-    </row>
-    <row r="41" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L40" s="36"/>
+    </row>
+    <row r="41" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="48">
+      <c r="B41" s="65">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="J41" s="37">
+      <c r="C41" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="G41" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="H41" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="I41" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J41" s="51">
         <v>1</v>
       </c>
-      <c r="K41" s="37">
-        <f t="shared" ref="K41" si="15">J41*5</f>
+      <c r="K41" s="51">
+        <f>J41*5</f>
         <v>5</v>
       </c>
-      <c r="L41" s="37"/>
-    </row>
-    <row r="42" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L41" s="55"/>
+    </row>
+    <row r="42" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="48">
+      <c r="B42" s="60">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="57" t="s">
+      <c r="C42" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D42" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="F42" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="G42" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="H42" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="I42" s="58" t="s">
+      <c r="D42" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G42" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="H42" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="I42" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="J42" s="58">
+      <c r="J42" s="36">
         <v>1</v>
       </c>
-      <c r="K42" s="58">
-        <f>J42*5</f>
+      <c r="K42" s="36">
+        <f t="shared" ref="K42" si="16">J42*5</f>
         <v>5</v>
       </c>
-      <c r="L42" s="62"/>
-    </row>
-    <row r="43" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L42" s="36"/>
+    </row>
+    <row r="43" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="48">
+      <c r="B43" s="65">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="J43" s="37">
+      <c r="D43" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="G43" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="H43" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="I43" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="J43" s="51">
         <v>1</v>
       </c>
-      <c r="K43" s="37">
-        <f t="shared" ref="K43:K44" si="16">J43*5</f>
+      <c r="K43" s="51">
+        <f>J43*5</f>
         <v>5</v>
       </c>
-      <c r="L43" s="37"/>
-    </row>
-    <row r="44" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L43" s="55"/>
+    </row>
+    <row r="44" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="48">
+      <c r="B44" s="60">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C44" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="H44" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I44" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="J44" s="36">
+        <v>1</v>
+      </c>
+      <c r="K44" s="36">
+        <f t="shared" ref="K44:K45" si="17">J44*5</f>
+        <v>5</v>
+      </c>
+      <c r="L44" s="36"/>
+    </row>
+    <row r="45" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="60">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="58" t="s">
+      <c r="D45" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="E44" s="58" t="s">
+      <c r="E45" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="58" t="s">
+      <c r="F45" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="G44" s="58" t="s">
+      <c r="G45" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="H44" s="58" t="s">
+      <c r="H45" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="I44" s="58" t="s">
+      <c r="I45" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="J44" s="58">
+      <c r="J45" s="51">
         <v>3</v>
       </c>
-      <c r="K44" s="58">
-        <f t="shared" si="16"/>
+      <c r="K45" s="51">
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
-      <c r="L44" s="62"/>
-    </row>
-    <row r="45" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="48">
-        <f>ROW(B45) - ROW($B$9)</f>
-        <v>36</v>
-      </c>
-      <c r="C45" s="59" t="s">
+      <c r="L45" s="55"/>
+    </row>
+    <row r="46" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="65">
+        <f>ROW(B46) - ROW($B$9)</f>
+        <v>37</v>
+      </c>
+      <c r="C46" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="60" t="s">
+      <c r="D46" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="37" t="s">
+      <c r="E46" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="F45" s="37" t="s">
+      <c r="F46" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="G45" s="37" t="s">
+      <c r="G46" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="H45" s="37" t="s">
+      <c r="H46" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="I45" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J45" s="37">
+      <c r="I46" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J46" s="36">
         <v>4</v>
       </c>
-      <c r="K45" s="37">
-        <f>J45*5</f>
+      <c r="K46" s="36">
+        <f>J46*5</f>
         <v>20</v>
       </c>
-      <c r="L45" s="37"/>
-    </row>
-    <row r="46" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="48">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="F46" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="G46" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="H46" s="58" t="s">
-        <v>287</v>
-      </c>
-      <c r="I46" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J46" s="58">
-        <v>1</v>
-      </c>
-      <c r="K46" s="58">
-        <f t="shared" ref="K46:K47" si="17">J46*5</f>
-        <v>5</v>
-      </c>
-      <c r="L46" s="62"/>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L46" s="36"/>
+    </row>
+    <row r="47" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="48">
+      <c r="B47" s="60">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="59" t="s">
+      <c r="C47" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J47" s="37">
+      <c r="D47" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="G47" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="H47" s="51" t="s">
+        <v>287</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J47" s="51">
         <v>1</v>
       </c>
-      <c r="K47" s="37">
-        <f t="shared" si="17"/>
+      <c r="K47" s="51">
+        <f t="shared" ref="K47:K48" si="18">J47*5</f>
         <v>5</v>
       </c>
-      <c r="L47" s="37"/>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L47" s="55"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="48">
+      <c r="B48" s="60">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="57" t="s">
-        <v>314</v>
-      </c>
-      <c r="D48" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="58" t="s">
-        <v>133</v>
-      </c>
-      <c r="F48" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="G48" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="H48" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="I48" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J48" s="58">
-        <v>6</v>
-      </c>
-      <c r="K48" s="58">
-        <f>J48*5</f>
-        <v>30</v>
-      </c>
-      <c r="L48" s="62"/>
-    </row>
-    <row r="49" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="F48" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="G48" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H48" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="I48" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J48" s="36">
+        <v>1</v>
+      </c>
+      <c r="K48" s="36">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="L48" s="36"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="48">
+      <c r="B49" s="65">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="60" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="G49" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="H49" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="I49" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J49" s="37">
-        <v>4</v>
-      </c>
-      <c r="K49" s="37">
-        <f t="shared" ref="K49" si="18">J49*5</f>
-        <v>20</v>
-      </c>
-      <c r="L49" s="37"/>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="66" t="s">
+        <v>314</v>
+      </c>
+      <c r="D49" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="F49" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="G49" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="H49" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="I49" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="J49" s="67">
+        <v>6</v>
+      </c>
+      <c r="K49" s="67">
+        <f>J49*5</f>
+        <v>30</v>
+      </c>
+      <c r="L49" s="67"/>
+    </row>
+    <row r="50" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="48">
+      <c r="B50" s="60">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="F50" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="G50" s="58" t="s">
-        <v>236</v>
-      </c>
-      <c r="H50" s="58" t="s">
-        <v>265</v>
-      </c>
-      <c r="I50" s="58" t="s">
-        <v>315</v>
-      </c>
-      <c r="J50" s="58">
-        <v>1</v>
-      </c>
-      <c r="K50" s="58">
-        <f>J50*5</f>
-        <v>5</v>
-      </c>
-      <c r="L50" s="62"/>
-    </row>
-    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="H50" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="I50" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J50" s="36">
+        <v>4</v>
+      </c>
+      <c r="K50" s="36">
+        <f t="shared" ref="K50" si="19">J50*5</f>
+        <v>20</v>
+      </c>
+      <c r="L50" s="36"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="48">
+      <c r="B51" s="65">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="59" t="s">
+      <c r="C51" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="F51" s="37" t="s">
+      <c r="D51" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G51" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="H51" s="37" t="s">
+      <c r="G51" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="H51" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I51" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="J51" s="37">
+      <c r="I51" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="J51" s="51">
         <v>1</v>
       </c>
-      <c r="K51" s="37">
-        <f t="shared" ref="K51" si="19">J51*5</f>
+      <c r="K51" s="51">
+        <f>J51*5</f>
         <v>5</v>
       </c>
-      <c r="L51" s="37"/>
-    </row>
-    <row r="52" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L51" s="55"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="48">
+      <c r="B52" s="60">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="F52" s="58" t="s">
+      <c r="D52" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="F52" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G52" s="58" t="s">
-        <v>238</v>
-      </c>
-      <c r="H52" s="58" t="s">
+      <c r="G52" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="H52" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I52" s="58" t="s">
-        <v>316</v>
-      </c>
-      <c r="J52" s="58">
-        <v>13</v>
-      </c>
-      <c r="K52" s="58">
-        <f>J52*5</f>
-        <v>65</v>
-      </c>
-      <c r="L52" s="62"/>
-    </row>
-    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I52" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="J52" s="36">
+        <v>1</v>
+      </c>
+      <c r="K52" s="36">
+        <f t="shared" ref="K52" si="20">J52*5</f>
+        <v>5</v>
+      </c>
+      <c r="L52" s="36"/>
+    </row>
+    <row r="53" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="48">
+      <c r="B53" s="65">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="59" t="s">
+      <c r="C53" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F53" s="37" t="s">
+      <c r="D53" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="F53" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G53" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="H53" s="37" t="s">
+      <c r="G53" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="H53" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I53" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="J53" s="37">
-        <v>1</v>
-      </c>
-      <c r="K53" s="37">
-        <f t="shared" ref="K53" si="20">J53*5</f>
-        <v>5</v>
-      </c>
-      <c r="L53" s="37"/>
-    </row>
-    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I53" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="J53" s="51">
+        <v>13</v>
+      </c>
+      <c r="K53" s="51">
+        <f>J53*5</f>
+        <v>65</v>
+      </c>
+      <c r="L53" s="55"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="48">
+      <c r="B54" s="60">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="E54" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="F54" s="58" t="s">
+      <c r="D54" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="F54" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G54" s="58" t="s">
-        <v>240</v>
-      </c>
-      <c r="H54" s="58" t="s">
+      <c r="G54" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="H54" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I54" s="58" t="s">
-        <v>318</v>
-      </c>
-      <c r="J54" s="58">
+      <c r="I54" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="J54" s="36">
         <v>1</v>
       </c>
-      <c r="K54" s="58">
-        <f>J54*5</f>
+      <c r="K54" s="36">
+        <f t="shared" ref="K54" si="21">J54*5</f>
         <v>5</v>
       </c>
-      <c r="L54" s="62"/>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L54" s="36"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="48">
+      <c r="B55" s="65">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="59" t="s">
+      <c r="C55" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="F55" s="37" t="s">
+      <c r="D55" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G55" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="H55" s="37" t="s">
+      <c r="G55" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="H55" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I55" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="J55" s="37">
-        <v>2</v>
-      </c>
-      <c r="K55" s="37">
-        <f t="shared" ref="K55" si="21">J55*5</f>
-        <v>10</v>
-      </c>
-      <c r="L55" s="37"/>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I55" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="J55" s="51">
+        <v>1</v>
+      </c>
+      <c r="K55" s="51">
+        <f>J55*5</f>
+        <v>5</v>
+      </c>
+      <c r="L55" s="55"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="48">
+      <c r="B56" s="60">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="E56" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="F56" s="58" t="s">
+      <c r="D56" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G56" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="H56" s="58" t="s">
+      <c r="G56" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="H56" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I56" s="58" t="s">
-        <v>320</v>
-      </c>
-      <c r="J56" s="58">
-        <v>3</v>
-      </c>
-      <c r="K56" s="58">
-        <f>J56*5</f>
-        <v>15</v>
-      </c>
-      <c r="L56" s="62"/>
-    </row>
-    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I56" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="J56" s="36">
+        <v>2</v>
+      </c>
+      <c r="K56" s="36">
+        <f t="shared" ref="K56" si="22">J56*5</f>
+        <v>10</v>
+      </c>
+      <c r="L56" s="36"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="48">
+      <c r="B57" s="65">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="59" t="s">
+      <c r="C57" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="F57" s="37" t="s">
+      <c r="D57" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="F57" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G57" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H57" s="37" t="s">
+      <c r="G57" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="H57" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I57" s="37" t="s">
-        <v>321</v>
-      </c>
-      <c r="J57" s="37">
-        <v>4</v>
-      </c>
-      <c r="K57" s="37">
-        <f t="shared" ref="K57" si="22">J57*5</f>
-        <v>20</v>
-      </c>
-      <c r="L57" s="37"/>
-    </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I57" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="J57" s="51">
+        <v>3</v>
+      </c>
+      <c r="K57" s="51">
+        <f>J57*5</f>
+        <v>15</v>
+      </c>
+      <c r="L57" s="55"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="48">
+      <c r="B58" s="60">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="E58" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="F58" s="58" t="s">
+      <c r="D58" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="F58" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G58" s="58" t="s">
-        <v>244</v>
-      </c>
-      <c r="H58" s="58" t="s">
+      <c r="G58" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I58" s="58" t="s">
-        <v>322</v>
-      </c>
-      <c r="J58" s="58">
-        <v>1</v>
-      </c>
-      <c r="K58" s="58">
-        <f>J58*5</f>
-        <v>5</v>
-      </c>
-      <c r="L58" s="62"/>
-    </row>
-    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="36" t="s">
+        <v>321</v>
+      </c>
+      <c r="J58" s="36">
+        <v>4</v>
+      </c>
+      <c r="K58" s="36">
+        <f t="shared" ref="K58" si="23">J58*5</f>
+        <v>20</v>
+      </c>
+      <c r="L58" s="36"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="48">
+      <c r="B59" s="65">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="59" t="s">
+      <c r="C59" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="F59" s="37" t="s">
+      <c r="D59" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="F59" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G59" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="H59" s="37" t="s">
+      <c r="G59" s="51" t="s">
+        <v>244</v>
+      </c>
+      <c r="H59" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I59" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="J59" s="37">
-        <v>3</v>
-      </c>
-      <c r="K59" s="37">
-        <f t="shared" ref="K59" si="23">J59*5</f>
-        <v>15</v>
-      </c>
-      <c r="L59" s="37"/>
-    </row>
-    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="J59" s="51">
+        <v>1</v>
+      </c>
+      <c r="K59" s="51">
+        <f>J59*5</f>
+        <v>5</v>
+      </c>
+      <c r="L59" s="55"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="48">
+      <c r="B60" s="60">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="F60" s="58" t="s">
+      <c r="D60" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="F60" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G60" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="H60" s="58" t="s">
+      <c r="G60" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="H60" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I60" s="58" t="s">
-        <v>324</v>
-      </c>
-      <c r="J60" s="58">
-        <v>6</v>
-      </c>
-      <c r="K60" s="58">
-        <f>J60*5</f>
-        <v>30</v>
-      </c>
-      <c r="L60" s="62"/>
-    </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="J60" s="36">
+        <v>3</v>
+      </c>
+      <c r="K60" s="36">
+        <f t="shared" ref="K60" si="24">J60*5</f>
+        <v>15</v>
+      </c>
+      <c r="L60" s="36"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="48">
+      <c r="B61" s="65">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="59" t="s">
+      <c r="C61" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F61" s="37" t="s">
+      <c r="D61" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="F61" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G61" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="H61" s="37" t="s">
+      <c r="G61" s="51" t="s">
+        <v>246</v>
+      </c>
+      <c r="H61" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I61" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="J61" s="37">
-        <v>4</v>
-      </c>
-      <c r="K61" s="37">
-        <f t="shared" ref="K61" si="24">J61*5</f>
-        <v>20</v>
-      </c>
-      <c r="L61" s="37"/>
-    </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="J61" s="51">
+        <v>6</v>
+      </c>
+      <c r="K61" s="51">
+        <f>J61*5</f>
+        <v>30</v>
+      </c>
+      <c r="L61" s="55"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="48">
+      <c r="B62" s="60">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="57" t="s">
+      <c r="C62" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="F62" s="58" t="s">
+      <c r="D62" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G62" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="H62" s="58" t="s">
+      <c r="G62" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="H62" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I62" s="58" t="s">
-        <v>326</v>
-      </c>
-      <c r="J62" s="58">
-        <v>1</v>
-      </c>
-      <c r="K62" s="58">
-        <f>J62*5</f>
-        <v>5</v>
-      </c>
-      <c r="L62" s="62"/>
-    </row>
-    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I62" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="J62" s="36">
+        <v>4</v>
+      </c>
+      <c r="K62" s="36">
+        <f t="shared" ref="K62" si="25">J62*5</f>
+        <v>20</v>
+      </c>
+      <c r="L62" s="36"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="48">
+      <c r="B63" s="65">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="59" t="s">
+      <c r="C63" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F63" s="37" t="s">
+      <c r="D63" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="F63" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G63" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="H63" s="37" t="s">
+      <c r="G63" s="51" t="s">
+        <v>248</v>
+      </c>
+      <c r="H63" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I63" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="J63" s="37">
-        <v>3</v>
-      </c>
-      <c r="K63" s="37">
-        <f t="shared" ref="K63" si="25">J63*5</f>
-        <v>15</v>
-      </c>
-      <c r="L63" s="37"/>
-    </row>
-    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I63" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="J63" s="51">
+        <v>1</v>
+      </c>
+      <c r="K63" s="51">
+        <f>J63*5</f>
+        <v>5</v>
+      </c>
+      <c r="L63" s="55"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="48">
+      <c r="B64" s="60">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="58" t="s">
-        <v>79</v>
-      </c>
-      <c r="E64" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="F64" s="58" t="s">
+      <c r="D64" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G64" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H64" s="58" t="s">
+      <c r="G64" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="H64" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I64" s="58" t="s">
-        <v>328</v>
-      </c>
-      <c r="J64" s="58">
-        <v>1</v>
-      </c>
-      <c r="K64" s="58">
-        <f>J64*5</f>
-        <v>5</v>
-      </c>
-      <c r="L64" s="62"/>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I64" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="J64" s="36">
+        <v>3</v>
+      </c>
+      <c r="K64" s="36">
+        <f t="shared" ref="K64" si="26">J64*5</f>
+        <v>15</v>
+      </c>
+      <c r="L64" s="36"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="48">
+      <c r="B65" s="65">
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="59" t="s">
+      <c r="C65" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="60" t="s">
-        <v>80</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F65" s="37" t="s">
+      <c r="D65" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="F65" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G65" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="H65" s="37" t="s">
+      <c r="G65" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="H65" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I65" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="J65" s="37">
+      <c r="I65" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="J65" s="51">
         <v>1</v>
       </c>
-      <c r="K65" s="37">
-        <f t="shared" ref="K65" si="26">J65*5</f>
+      <c r="K65" s="51">
+        <f>J65*5</f>
         <v>5</v>
       </c>
-      <c r="L65" s="37"/>
-    </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L65" s="55"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="48">
+      <c r="B66" s="60">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="58" t="s">
-        <v>81</v>
-      </c>
-      <c r="E66" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F66" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="G66" s="58" t="s">
-        <v>252</v>
-      </c>
-      <c r="H66" s="58" t="s">
+      <c r="D66" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="G66" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="H66" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I66" s="58" t="s">
-        <v>323</v>
-      </c>
-      <c r="J66" s="58">
+      <c r="I66" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="J66" s="36">
         <v>1</v>
       </c>
-      <c r="K66" s="58">
-        <f>J66*5</f>
+      <c r="K66" s="36">
+        <f t="shared" ref="K66" si="27">J66*5</f>
         <v>5</v>
       </c>
-      <c r="L66" s="62"/>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L66" s="36"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="48">
+      <c r="B67" s="65">
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="F67" s="37" t="s">
+      <c r="D67" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="F67" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="G67" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="H67" s="37" t="s">
+      <c r="G67" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="H67" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="I67" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J67" s="37">
+      <c r="I67" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="J67" s="51">
         <v>1</v>
       </c>
-      <c r="K67" s="37">
-        <f t="shared" ref="K67" si="27">J67*5</f>
+      <c r="K67" s="51">
+        <f>J67*5</f>
         <v>5</v>
       </c>
-      <c r="L67" s="37"/>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L67" s="55"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="48">
+      <c r="B68" s="60">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="D68" s="58" t="s">
-        <v>83</v>
-      </c>
-      <c r="E68" s="58" t="s">
-        <v>153</v>
-      </c>
-      <c r="F68" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="G68" s="58" t="s">
-        <v>197</v>
-      </c>
-      <c r="H68" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="I68" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J68" s="58">
-        <v>2</v>
-      </c>
-      <c r="K68" s="58">
-        <f>J68*5</f>
-        <v>10</v>
-      </c>
-      <c r="L68" s="62"/>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="F68" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="G68" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="H68" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="I68" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="J68" s="36">
+        <v>1</v>
+      </c>
+      <c r="K68" s="36">
+        <f t="shared" ref="K68" si="28">J68*5</f>
+        <v>5</v>
+      </c>
+      <c r="L68" s="36"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="48">
+      <c r="B69" s="65">
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="59" t="s">
-        <v>339</v>
-      </c>
-      <c r="D69" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="F69" s="37" t="s">
+      <c r="C69" s="66" t="s">
         <v>337</v>
       </c>
-      <c r="G69" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J69" s="37">
-        <v>1</v>
-      </c>
-      <c r="K69" s="37">
-        <f t="shared" ref="K69" si="28">J69*5</f>
-        <v>5</v>
-      </c>
-      <c r="L69" s="37"/>
-    </row>
-    <row r="70" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="F69" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="G69" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="I69" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="J69" s="67">
+        <v>2</v>
+      </c>
+      <c r="K69" s="67">
+        <f>J69*5</f>
+        <v>10</v>
+      </c>
+      <c r="L69" s="67"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="48">
+      <c r="B70" s="60">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="E70" s="58" t="s">
-        <v>155</v>
-      </c>
-      <c r="F70" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="G70" s="58" t="s">
-        <v>255</v>
-      </c>
-      <c r="H70" s="58" t="s">
-        <v>291</v>
-      </c>
-      <c r="I70" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J70" s="58">
+      <c r="C70" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="E70" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F70" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="G70" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="H70" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="I70" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J70" s="36">
         <v>1</v>
       </c>
-      <c r="K70" s="58">
-        <f>J70*5</f>
+      <c r="K70" s="36">
+        <f t="shared" ref="K70" si="29">J70*5</f>
         <v>5</v>
       </c>
-      <c r="L70" s="62"/>
-    </row>
-    <row r="71" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L70" s="36"/>
+    </row>
+    <row r="71" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="48">
+      <c r="B71" s="65">
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="59" t="s">
+      <c r="C71" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="60" t="s">
-        <v>86</v>
-      </c>
-      <c r="E71" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="G71" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J71" s="37">
+      <c r="D71" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="F71" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="G71" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="H71" s="51" t="s">
+        <v>291</v>
+      </c>
+      <c r="I71" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J71" s="51">
         <v>1</v>
       </c>
-      <c r="K71" s="37">
-        <f t="shared" ref="K71" si="29">J71*5</f>
+      <c r="K71" s="51">
+        <f>J71*5</f>
         <v>5</v>
       </c>
-      <c r="L71" s="37"/>
-    </row>
-    <row r="72" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L71" s="55"/>
+    </row>
+    <row r="72" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="48">
+      <c r="B72" s="60">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="57" t="s">
+      <c r="C72" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="E72" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="F72" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="G72" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="H72" s="58" t="s">
-        <v>293</v>
-      </c>
-      <c r="I72" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J72" s="58">
+      <c r="D72" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E72" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="F72" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="G72" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="H72" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="I72" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J72" s="36">
         <v>1</v>
       </c>
-      <c r="K72" s="58">
-        <f>J72*5</f>
+      <c r="K72" s="36">
+        <f t="shared" ref="K72" si="30">J72*5</f>
         <v>5</v>
       </c>
-      <c r="L72" s="62"/>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L72" s="36"/>
+    </row>
+    <row r="73" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="48">
+      <c r="B73" s="65">
         <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="59" t="s">
+      <c r="C73" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J73" s="37">
-        <v>4</v>
-      </c>
-      <c r="K73" s="37">
-        <f t="shared" ref="K73" si="30">J73*5</f>
-        <v>20</v>
-      </c>
-      <c r="L73" s="37"/>
-    </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="F73" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="G73" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="H73" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="I73" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J73" s="51">
+        <v>1</v>
+      </c>
+      <c r="K73" s="51">
+        <f>J73*5</f>
+        <v>5</v>
+      </c>
+      <c r="L73" s="55"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="48">
+      <c r="B74" s="60">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="57" t="s">
+      <c r="C74" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="E74" s="58" t="s">
-        <v>159</v>
-      </c>
-      <c r="F74" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="G74" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="H74" s="58" t="s">
-        <v>295</v>
-      </c>
-      <c r="I74" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J74" s="58">
-        <v>2</v>
-      </c>
-      <c r="K74" s="58">
-        <f>J74*5</f>
-        <v>10</v>
-      </c>
-      <c r="L74" s="62"/>
-    </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E74" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F74" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="G74" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="H74" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="I74" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J74" s="36">
+        <v>4</v>
+      </c>
+      <c r="K74" s="36">
+        <f t="shared" ref="K74" si="31">J74*5</f>
+        <v>20</v>
+      </c>
+      <c r="L74" s="36"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="48">
+      <c r="B75" s="65">
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="59" t="s">
+      <c r="C75" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D75" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="E75" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="F75" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="H75" s="37" t="s">
+      <c r="D75" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="E75" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="F75" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="G75" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="H75" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="I75" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J75" s="37">
-        <v>1</v>
-      </c>
-      <c r="K75" s="37">
-        <f t="shared" ref="K75" si="31">J75*5</f>
-        <v>5</v>
-      </c>
-      <c r="L75" s="37"/>
-    </row>
-    <row r="76" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I75" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J75" s="51">
+        <v>2</v>
+      </c>
+      <c r="K75" s="51">
+        <f>J75*5</f>
+        <v>10</v>
+      </c>
+      <c r="L75" s="55"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="48">
+      <c r="B76" s="60">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="D76" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="E76" s="58" t="s">
-        <v>161</v>
-      </c>
-      <c r="F76" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="G76" s="58" t="s">
-        <v>203</v>
-      </c>
-      <c r="H76" s="58" t="s">
-        <v>296</v>
-      </c>
-      <c r="I76" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J76" s="58">
+      <c r="C76" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="F76" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="G76" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="H76" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="I76" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J76" s="36">
         <v>1</v>
       </c>
-      <c r="K76" s="58">
-        <f>J76*5</f>
+      <c r="K76" s="36">
+        <f t="shared" ref="K76" si="32">J76*5</f>
         <v>5</v>
       </c>
-      <c r="L76" s="62"/>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L76" s="36"/>
+    </row>
+    <row r="77" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="48">
+      <c r="B77" s="65">
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D77" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="G77" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="H77" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J77" s="37">
+      <c r="C77" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="F77" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="G77" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="H77" s="51" t="s">
+        <v>296</v>
+      </c>
+      <c r="I77" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J77" s="51">
         <v>1</v>
       </c>
-      <c r="K77" s="37">
-        <f t="shared" ref="K77" si="32">J77*5</f>
+      <c r="K77" s="51">
+        <f>J77*5</f>
         <v>5</v>
       </c>
-      <c r="L77" s="37"/>
-    </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L77" s="55"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="48">
+      <c r="B78" s="60">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="57" t="s">
+      <c r="C78" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D78" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="E78" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="F78" s="58" t="s">
-        <v>205</v>
-      </c>
-      <c r="G78" s="58" t="s">
-        <v>262</v>
-      </c>
-      <c r="H78" s="58" t="s">
-        <v>298</v>
-      </c>
-      <c r="I78" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="J78" s="58">
+      <c r="D78" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="F78" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="G78" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="H78" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="I78" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J78" s="36">
         <v>1</v>
       </c>
-      <c r="K78" s="58">
-        <f>J78*5</f>
+      <c r="K78" s="36">
+        <f t="shared" ref="K78" si="33">J78*5</f>
         <v>5</v>
       </c>
-      <c r="L78" s="62"/>
-    </row>
-    <row r="79" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L78" s="36"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="48">
+      <c r="B79" s="65">
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="59" t="s">
+      <c r="C79" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E79" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="F79" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="G79" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="H79" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="I79" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="J79" s="51">
+        <v>1</v>
+      </c>
+      <c r="K79" s="51">
+        <f>J79*5</f>
+        <v>5</v>
+      </c>
+      <c r="L79" s="55"/>
+    </row>
+    <row r="80" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="60">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="C80" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D79" s="60" t="s">
+      <c r="D80" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="E79" s="37" t="s">
+      <c r="E80" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="F79" s="37" t="s">
+      <c r="F80" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="G79" s="37" t="s">
+      <c r="G80" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="H79" s="37" t="s">
+      <c r="H80" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="I79" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J79" s="37">
+      <c r="I80" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J80" s="36">
         <v>1</v>
       </c>
-      <c r="K79" s="37">
-        <f t="shared" ref="K79" si="33">J79*5</f>
+      <c r="K80" s="36">
+        <f t="shared" ref="K80:K83" si="34">J80*5</f>
         <v>5</v>
       </c>
-      <c r="L79" s="37"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="31"/>
-      <c r="C80" s="46"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="33"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="34"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="35"/>
-      <c r="L80" s="39"/>
-    </row>
-    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L80" s="36"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="24"/>
-      <c r="C81" s="47"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="40"/>
+      <c r="B81" s="60">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C81" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D81" s="62" t="s">
+        <v>350</v>
+      </c>
+      <c r="E81" s="63" t="s">
+        <v>351</v>
+      </c>
+      <c r="F81" s="63" t="s">
+        <v>333</v>
+      </c>
+      <c r="G81" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="H81" s="63" t="s">
+        <v>353</v>
+      </c>
+      <c r="I81" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="J81" s="63">
+        <v>1</v>
+      </c>
+      <c r="K81" s="63">
+        <f t="shared" si="34"/>
+        <v>5</v>
+      </c>
+      <c r="L81" s="63"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="60">
+        <f t="shared" ref="B82:B83" si="35">ROW(B82) - ROW($B$9)</f>
+        <v>73</v>
+      </c>
+      <c r="C82" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="D82" s="64" t="s">
+        <v>350</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="F82" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G82" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="H82" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="I82" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J82" s="36">
+        <v>1</v>
+      </c>
+      <c r="K82" s="36">
+        <f t="shared" si="34"/>
+        <v>5</v>
+      </c>
+      <c r="L82" s="36"/>
+    </row>
+    <row r="83" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1"/>
+      <c r="B83" s="70">
+        <f t="shared" si="35"/>
+        <v>74</v>
+      </c>
+      <c r="C83" s="71" t="s">
+        <v>349</v>
+      </c>
+      <c r="D83" s="72" t="s">
+        <v>350</v>
+      </c>
+      <c r="E83" s="68" t="s">
+        <v>356</v>
+      </c>
+      <c r="F83" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="G83" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="H83" s="68" t="s">
+        <v>353</v>
+      </c>
+      <c r="I83" s="68" t="s">
+        <v>336</v>
+      </c>
+      <c r="J83" s="68">
+        <v>1</v>
+      </c>
+      <c r="K83" s="68">
+        <f t="shared" si="34"/>
+        <v>5</v>
+      </c>
+      <c r="L83" s="68"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="43"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="34"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="34"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="35"/>
+      <c r="L84" s="73"/>
+    </row>
+    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="24"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BOM/Client-BOM.xlsx
+++ b/BOM/Client-BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C8D166-3906-4D2C-8E02-2C7A50C0213B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C35280-50FE-49E7-BDC2-AE55C7835570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="363">
   <si>
     <t>Component list</t>
   </si>
@@ -1058,9 +1058,6 @@
   </si>
   <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less Stock On LCSC </t>
   </si>
   <si>
     <t>Bill of Materials for Project [Mega2560_Custom]</t>
@@ -1550,7 +1547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1702,6 +1699,60 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1710,66 +1761,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2137,10 +2128,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2151,7 +2142,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="46" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2169,14 +2160,14 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="47" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="58"/>
+      <c r="L3" s="76"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2187,14 +2178,14 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="48" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="59"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2212,7 +2203,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="59"/>
+      <c r="L5" s="77"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2226,7 +2217,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="59"/>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2240,7 +2231,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="59"/>
+      <c r="L7" s="77"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2254,7 +2245,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="59"/>
+      <c r="L8" s="77"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2294,403 +2285,403 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="65">
+      <c r="B10" s="61">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="77" t="s">
+      <c r="C10" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="76" t="s">
+      <c r="G10" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="H10" s="76" t="s">
+      <c r="H10" s="71" t="s">
         <v>265</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="71" t="s">
         <v>300</v>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="71">
         <v>1</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="71">
         <f>J10*5</f>
         <v>5</v>
       </c>
-      <c r="L10" s="76"/>
+      <c r="L10" s="71"/>
     </row>
     <row r="11" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="60">
-        <f t="shared" ref="B11:B81" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="61">
+        <f t="shared" ref="B11:B74" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="63" t="s">
+      <c r="F11" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="69" t="s">
         <v>339</v>
       </c>
-      <c r="H11" s="63" t="s">
+      <c r="H11" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="59" t="s">
         <v>301</v>
       </c>
-      <c r="J11" s="63">
+      <c r="J11" s="59">
         <v>28</v>
       </c>
-      <c r="K11" s="63">
+      <c r="K11" s="59">
         <f t="shared" ref="K11" si="1">J11*5</f>
         <v>140</v>
       </c>
-      <c r="L11" s="63"/>
+      <c r="L11" s="59"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="65">
-        <f>ROW(B12) - ROW($B$9)</f>
+      <c r="B12" s="61">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="78" t="s">
+      <c r="D12" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="73" t="s">
         <v>332</v>
       </c>
-      <c r="F12" s="78" t="s">
+      <c r="F12" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="G12" s="78" t="s">
+      <c r="G12" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="H12" s="78" t="s">
+      <c r="H12" s="73" t="s">
         <v>340</v>
       </c>
-      <c r="I12" s="78" t="s">
+      <c r="I12" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="J12" s="78">
+      <c r="J12" s="73">
         <v>2</v>
       </c>
-      <c r="K12" s="78">
+      <c r="K12" s="73">
         <f>J12*5</f>
         <v>10</v>
       </c>
-      <c r="L12" s="79"/>
+      <c r="L12" s="74"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="60">
+      <c r="B13" s="61">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="74" t="s">
-        <v>358</v>
-      </c>
-      <c r="E13" s="63" t="s">
+      <c r="D13" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="E13" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="F13" s="63" t="s">
+      <c r="F13" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="H13" s="63" t="s">
+      <c r="H13" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="I13" s="63" t="s">
+      <c r="I13" s="59" t="s">
         <v>303</v>
       </c>
-      <c r="J13" s="63">
+      <c r="J13" s="59">
         <v>3</v>
       </c>
-      <c r="K13" s="63">
+      <c r="K13" s="59">
         <f t="shared" ref="K13:K14" si="2">J13*5</f>
         <v>15</v>
       </c>
-      <c r="L13" s="75"/>
+      <c r="L13" s="70"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="60">
+      <c r="B14" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="78" t="s">
+      <c r="G14" s="73" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="73" t="s">
         <v>266</v>
       </c>
-      <c r="I14" s="78" t="s">
+      <c r="I14" s="73" t="s">
         <v>304</v>
       </c>
-      <c r="J14" s="78">
+      <c r="J14" s="73">
         <v>1</v>
       </c>
-      <c r="K14" s="78">
+      <c r="K14" s="73">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L14" s="79"/>
+      <c r="L14" s="74"/>
     </row>
     <row r="15" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="65">
-        <f>ROW(B15) - ROW($B$9)</f>
+      <c r="B15" s="61">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="63" t="s">
+      <c r="F15" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="63" t="s">
+      <c r="H15" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="I15" s="63" t="s">
+      <c r="I15" s="59" t="s">
         <v>305</v>
       </c>
-      <c r="J15" s="63">
+      <c r="J15" s="59">
         <v>12</v>
       </c>
-      <c r="K15" s="63">
+      <c r="K15" s="59">
         <f>J15*5</f>
         <v>60</v>
       </c>
-      <c r="L15" s="63"/>
+      <c r="L15" s="59"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="60">
+      <c r="B16" s="61">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="77" t="s">
+      <c r="C16" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="78" t="s">
+      <c r="D16" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="73" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="78" t="s">
+      <c r="F16" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="G16" s="78" t="s">
+      <c r="G16" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="73" t="s">
         <v>265</v>
       </c>
-      <c r="I16" s="78" t="s">
+      <c r="I16" s="73" t="s">
         <v>306</v>
       </c>
-      <c r="J16" s="78">
+      <c r="J16" s="73">
         <v>1</v>
       </c>
-      <c r="K16" s="78">
+      <c r="K16" s="73">
         <f t="shared" ref="K16" si="3">J16*5</f>
         <v>5</v>
       </c>
-      <c r="L16" s="79"/>
+      <c r="L16" s="74"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="65">
-        <f>ROW(B17) - ROW($B$9)</f>
+      <c r="B17" s="61">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="G17" s="74" t="s">
-        <v>363</v>
-      </c>
-      <c r="H17" s="63" t="s">
+      <c r="G17" s="69" t="s">
+        <v>362</v>
+      </c>
+      <c r="H17" s="59" t="s">
         <v>267</v>
       </c>
-      <c r="I17" s="63" t="s">
+      <c r="I17" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="J17" s="63">
+      <c r="J17" s="59">
         <v>1</v>
       </c>
-      <c r="K17" s="63">
+      <c r="K17" s="59">
         <f>J17*5</f>
         <v>5</v>
       </c>
-      <c r="L17" s="63"/>
+      <c r="L17" s="59"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="60">
+      <c r="B18" s="61">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="77" t="s">
+      <c r="C18" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="78" t="s">
+      <c r="D18" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="78" t="s">
+      <c r="F18" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="G18" s="78" t="s">
+      <c r="G18" s="73" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="78" t="s">
+      <c r="H18" s="73" t="s">
         <v>265</v>
       </c>
-      <c r="I18" s="78" t="s">
+      <c r="I18" s="73" t="s">
         <v>308</v>
       </c>
-      <c r="J18" s="78">
+      <c r="J18" s="73">
         <v>2</v>
       </c>
-      <c r="K18" s="78">
+      <c r="K18" s="73">
         <f t="shared" ref="K18" si="4">J18*5</f>
         <v>10</v>
       </c>
-      <c r="L18" s="79"/>
+      <c r="L18" s="74"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="65">
-        <f>ROW(B19) - ROW($B$9)</f>
+      <c r="B19" s="61">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="63" t="s">
+      <c r="F19" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="G19" s="63" t="s">
+      <c r="G19" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="H19" s="63" t="s">
+      <c r="H19" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="I19" s="63" t="s">
+      <c r="I19" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="J19" s="63">
+      <c r="J19" s="59">
         <v>2</v>
       </c>
-      <c r="K19" s="63">
+      <c r="K19" s="59">
         <f>J19*5</f>
         <v>10</v>
       </c>
-      <c r="L19" s="63"/>
+      <c r="L19" s="59"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="65">
-        <f>ROW(B20) - ROW($B$9)</f>
+      <c r="B20" s="61">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="71" t="s">
+        <v>358</v>
+      </c>
+      <c r="E20" s="71" t="s">
         <v>359</v>
       </c>
-      <c r="E20" s="76" t="s">
+      <c r="F20" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="G20" s="71" t="s">
         <v>360</v>
       </c>
-      <c r="F20" s="76" t="s">
-        <v>333</v>
-      </c>
-      <c r="G20" s="76" t="s">
+      <c r="H20" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="I20" s="71" t="s">
         <v>361</v>
       </c>
-      <c r="H20" s="76" t="s">
-        <v>266</v>
-      </c>
-      <c r="I20" s="76" t="s">
-        <v>362</v>
-      </c>
-      <c r="J20" s="76">
+      <c r="J20" s="71">
         <v>1</v>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="71">
         <f>J20*5</f>
         <v>5</v>
       </c>
-      <c r="L20" s="76"/>
+      <c r="L20" s="71"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="60">
+      <c r="B21" s="61">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2726,8 +2717,8 @@
     </row>
     <row r="22" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="65">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="61">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="52" t="s">
@@ -2762,7 +2753,7 @@
     </row>
     <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="60">
+      <c r="B23" s="61">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2798,8 +2789,8 @@
     </row>
     <row r="24" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="65">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="61">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="52" t="s">
@@ -2834,7 +2825,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="60">
+      <c r="B25" s="61">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -2870,8 +2861,8 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="65">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="61">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="52" t="s">
@@ -2906,7 +2897,7 @@
     </row>
     <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="60">
+      <c r="B27" s="61">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -2942,8 +2933,8 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="65">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="61">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="52" t="s">
@@ -2978,7 +2969,7 @@
     </row>
     <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="60">
+      <c r="B29" s="61">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3014,8 +3005,8 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="65">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="61">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="52" t="s">
@@ -3050,7 +3041,7 @@
     </row>
     <row r="31" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="60">
+      <c r="B31" s="61">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3086,8 +3077,8 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="65">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="61">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="52" t="s">
@@ -3122,7 +3113,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="60">
+      <c r="B33" s="61">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3158,8 +3149,8 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="65">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="61">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="52" t="s">
@@ -3194,8 +3185,8 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="60">
-        <f t="shared" ref="B35" si="12">ROW(B35) - ROW($B$9)</f>
+      <c r="B35" s="61">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="50" t="s">
@@ -3223,14 +3214,14 @@
         <v>1</v>
       </c>
       <c r="K35" s="51">
-        <f t="shared" ref="K35:K36" si="13">J35*5</f>
+        <f t="shared" ref="K35:K36" si="12">J35*5</f>
         <v>5</v>
       </c>
       <c r="L35" s="55"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="60">
+      <c r="B36" s="61">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -3259,17 +3250,15 @@
         <v>6</v>
       </c>
       <c r="K36" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="L36" s="56" t="s">
-        <v>346</v>
-      </c>
+      <c r="L36" s="56"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="65">
-        <f>ROW(B37) - ROW($B$9)</f>
+      <c r="B37" s="61">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="50" t="s">
@@ -3304,7 +3293,7 @@
     </row>
     <row r="38" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="60">
+      <c r="B38" s="61">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -3333,15 +3322,15 @@
         <v>1</v>
       </c>
       <c r="K38" s="36">
-        <f t="shared" ref="K38" si="14">J38*5</f>
+        <f t="shared" ref="K38" si="13">J38*5</f>
         <v>5</v>
       </c>
       <c r="L38" s="36"/>
     </row>
     <row r="39" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="65">
-        <f>ROW(B39) - ROW($B$9)</f>
+      <c r="B39" s="61">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="50" t="s">
@@ -3376,7 +3365,7 @@
     </row>
     <row r="40" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="60">
+      <c r="B40" s="61">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -3405,15 +3394,15 @@
         <v>1</v>
       </c>
       <c r="K40" s="36">
-        <f t="shared" ref="K40" si="15">J40*5</f>
+        <f t="shared" ref="K40" si="14">J40*5</f>
         <v>5</v>
       </c>
       <c r="L40" s="36"/>
     </row>
     <row r="41" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="65">
-        <f>ROW(B41) - ROW($B$9)</f>
+      <c r="B41" s="61">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="50" t="s">
@@ -3448,7 +3437,7 @@
     </row>
     <row r="42" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="60">
+      <c r="B42" s="61">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -3477,15 +3466,15 @@
         <v>1</v>
       </c>
       <c r="K42" s="36">
-        <f t="shared" ref="K42" si="16">J42*5</f>
+        <f t="shared" ref="K42" si="15">J42*5</f>
         <v>5</v>
       </c>
       <c r="L42" s="36"/>
     </row>
     <row r="43" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="65">
-        <f>ROW(B43) - ROW($B$9)</f>
+      <c r="B43" s="61">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C43" s="50" t="s">
@@ -3520,7 +3509,7 @@
     </row>
     <row r="44" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="60">
+      <c r="B44" s="61">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -3549,14 +3538,14 @@
         <v>1</v>
       </c>
       <c r="K44" s="36">
-        <f t="shared" ref="K44:K45" si="17">J44*5</f>
+        <f t="shared" ref="K44:K45" si="16">J44*5</f>
         <v>5</v>
       </c>
       <c r="L44" s="36"/>
     </row>
     <row r="45" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="60">
+      <c r="B45" s="61">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -3585,15 +3574,15 @@
         <v>3</v>
       </c>
       <c r="K45" s="51">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="L45" s="55"/>
     </row>
     <row r="46" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="65">
-        <f>ROW(B46) - ROW($B$9)</f>
+      <c r="B46" s="61">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="52" t="s">
@@ -3628,8 +3617,8 @@
     </row>
     <row r="47" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="60">
-        <f>ROW(B47) - ROW($B$9)</f>
+      <c r="B47" s="61">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="C47" s="50" t="s">
@@ -3657,14 +3646,14 @@
         <v>1</v>
       </c>
       <c r="K47" s="51">
-        <f t="shared" ref="K47:K48" si="18">J47*5</f>
+        <f t="shared" ref="K47:K48" si="17">J47*5</f>
         <v>5</v>
       </c>
       <c r="L47" s="55"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="60">
+      <c r="B48" s="61">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -3693,50 +3682,50 @@
         <v>1</v>
       </c>
       <c r="K48" s="36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="L48" s="36"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="65">
-        <f>ROW(B49) - ROW($B$9)</f>
+      <c r="B49" s="61">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="66" t="s">
+      <c r="C49" s="62" t="s">
         <v>314</v>
       </c>
-      <c r="D49" s="67" t="s">
+      <c r="D49" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="E49" s="67" t="s">
+      <c r="E49" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="F49" s="67" t="s">
+      <c r="F49" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="G49" s="67" t="s">
+      <c r="G49" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="67" t="s">
+      <c r="H49" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="I49" s="67" t="s">
+      <c r="I49" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="J49" s="67">
+      <c r="J49" s="63">
         <v>6</v>
       </c>
-      <c r="K49" s="67">
+      <c r="K49" s="63">
         <f>J49*5</f>
         <v>30</v>
       </c>
-      <c r="L49" s="67"/>
+      <c r="L49" s="63"/>
     </row>
     <row r="50" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="60">
+      <c r="B50" s="61">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -3765,15 +3754,15 @@
         <v>4</v>
       </c>
       <c r="K50" s="36">
-        <f t="shared" ref="K50" si="19">J50*5</f>
+        <f t="shared" ref="K50" si="18">J50*5</f>
         <v>20</v>
       </c>
       <c r="L50" s="36"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="65">
-        <f>ROW(B51) - ROW($B$9)</f>
+      <c r="B51" s="61">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C51" s="50" t="s">
@@ -3808,7 +3797,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="60">
+      <c r="B52" s="61">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -3837,15 +3826,15 @@
         <v>1</v>
       </c>
       <c r="K52" s="36">
-        <f t="shared" ref="K52" si="20">J52*5</f>
+        <f t="shared" ref="K52" si="19">J52*5</f>
         <v>5</v>
       </c>
       <c r="L52" s="36"/>
     </row>
     <row r="53" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="65">
-        <f>ROW(B53) - ROW($B$9)</f>
+      <c r="B53" s="61">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C53" s="50" t="s">
@@ -3880,7 +3869,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="60">
+      <c r="B54" s="61">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -3909,15 +3898,15 @@
         <v>1</v>
       </c>
       <c r="K54" s="36">
-        <f t="shared" ref="K54" si="21">J54*5</f>
+        <f t="shared" ref="K54" si="20">J54*5</f>
         <v>5</v>
       </c>
       <c r="L54" s="36"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="65">
-        <f>ROW(B55) - ROW($B$9)</f>
+      <c r="B55" s="61">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C55" s="50" t="s">
@@ -3952,7 +3941,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="60">
+      <c r="B56" s="61">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -3981,15 +3970,15 @@
         <v>2</v>
       </c>
       <c r="K56" s="36">
-        <f t="shared" ref="K56" si="22">J56*5</f>
+        <f t="shared" ref="K56" si="21">J56*5</f>
         <v>10</v>
       </c>
       <c r="L56" s="36"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="65">
-        <f>ROW(B57) - ROW($B$9)</f>
+      <c r="B57" s="61">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="C57" s="50" t="s">
@@ -4024,7 +4013,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="60">
+      <c r="B58" s="61">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -4053,15 +4042,15 @@
         <v>4</v>
       </c>
       <c r="K58" s="36">
-        <f t="shared" ref="K58" si="23">J58*5</f>
+        <f t="shared" ref="K58" si="22">J58*5</f>
         <v>20</v>
       </c>
       <c r="L58" s="36"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="65">
-        <f>ROW(B59) - ROW($B$9)</f>
+      <c r="B59" s="61">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="C59" s="50" t="s">
@@ -4096,7 +4085,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="60">
+      <c r="B60" s="61">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -4125,15 +4114,15 @@
         <v>3</v>
       </c>
       <c r="K60" s="36">
-        <f t="shared" ref="K60" si="24">J60*5</f>
+        <f t="shared" ref="K60" si="23">J60*5</f>
         <v>15</v>
       </c>
       <c r="L60" s="36"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="65">
-        <f>ROW(B61) - ROW($B$9)</f>
+      <c r="B61" s="61">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="C61" s="50" t="s">
@@ -4168,7 +4157,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="60">
+      <c r="B62" s="61">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
@@ -4197,15 +4186,15 @@
         <v>4</v>
       </c>
       <c r="K62" s="36">
-        <f t="shared" ref="K62" si="25">J62*5</f>
+        <f t="shared" ref="K62" si="24">J62*5</f>
         <v>20</v>
       </c>
       <c r="L62" s="36"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="65">
-        <f>ROW(B63) - ROW($B$9)</f>
+      <c r="B63" s="61">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C63" s="50" t="s">
@@ -4240,7 +4229,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="60">
+      <c r="B64" s="61">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -4269,15 +4258,15 @@
         <v>3</v>
       </c>
       <c r="K64" s="36">
-        <f t="shared" ref="K64" si="26">J64*5</f>
+        <f t="shared" ref="K64" si="25">J64*5</f>
         <v>15</v>
       </c>
       <c r="L64" s="36"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="65">
-        <f>ROW(B65) - ROW($B$9)</f>
+      <c r="B65" s="61">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C65" s="50" t="s">
@@ -4312,7 +4301,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="60">
+      <c r="B66" s="61">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -4341,15 +4330,15 @@
         <v>1</v>
       </c>
       <c r="K66" s="36">
-        <f t="shared" ref="K66" si="27">J66*5</f>
+        <f t="shared" ref="K66" si="26">J66*5</f>
         <v>5</v>
       </c>
       <c r="L66" s="36"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="65">
-        <f>ROW(B67) - ROW($B$9)</f>
+      <c r="B67" s="61">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C67" s="50" t="s">
@@ -4384,7 +4373,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="60">
+      <c r="B68" s="61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
@@ -4413,50 +4402,50 @@
         <v>1</v>
       </c>
       <c r="K68" s="36">
-        <f t="shared" ref="K68" si="28">J68*5</f>
+        <f t="shared" ref="K68" si="27">J68*5</f>
         <v>5</v>
       </c>
       <c r="L68" s="36"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="65">
-        <f>ROW(B69) - ROW($B$9)</f>
+      <c r="B69" s="61">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="66" t="s">
+      <c r="C69" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="D69" s="67" t="s">
+      <c r="D69" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="E69" s="67" t="s">
+      <c r="E69" s="63" t="s">
         <v>153</v>
       </c>
-      <c r="F69" s="67" t="s">
+      <c r="F69" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="G69" s="67" t="s">
+      <c r="G69" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="H69" s="67" t="s">
+      <c r="H69" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="I69" s="67" t="s">
+      <c r="I69" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="J69" s="67">
+      <c r="J69" s="63">
         <v>2</v>
       </c>
-      <c r="K69" s="67">
+      <c r="K69" s="63">
         <f>J69*5</f>
         <v>10</v>
       </c>
-      <c r="L69" s="67"/>
+      <c r="L69" s="63"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="60">
+      <c r="B70" s="61">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -4485,15 +4474,15 @@
         <v>1</v>
       </c>
       <c r="K70" s="36">
-        <f t="shared" ref="K70" si="29">J70*5</f>
+        <f t="shared" ref="K70" si="28">J70*5</f>
         <v>5</v>
       </c>
       <c r="L70" s="36"/>
     </row>
     <row r="71" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="65">
-        <f>ROW(B71) - ROW($B$9)</f>
+      <c r="B71" s="61">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C71" s="50" t="s">
@@ -4528,7 +4517,7 @@
     </row>
     <row r="72" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="60">
+      <c r="B72" s="61">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
@@ -4557,15 +4546,15 @@
         <v>1</v>
       </c>
       <c r="K72" s="36">
-        <f t="shared" ref="K72" si="30">J72*5</f>
+        <f t="shared" ref="K72" si="29">J72*5</f>
         <v>5</v>
       </c>
       <c r="L72" s="36"/>
     </row>
     <row r="73" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="65">
-        <f>ROW(B73) - ROW($B$9)</f>
+      <c r="B73" s="61">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C73" s="50" t="s">
@@ -4600,7 +4589,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="60">
+      <c r="B74" s="61">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
@@ -4629,15 +4618,15 @@
         <v>4</v>
       </c>
       <c r="K74" s="36">
-        <f t="shared" ref="K74" si="31">J74*5</f>
+        <f t="shared" ref="K74" si="30">J74*5</f>
         <v>20</v>
       </c>
       <c r="L74" s="36"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="65">
-        <f>ROW(B75) - ROW($B$9)</f>
+      <c r="B75" s="61">
+        <f t="shared" ref="B75:B83" si="31">ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
       <c r="C75" s="50" t="s">
@@ -4672,8 +4661,8 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="60">
-        <f t="shared" si="0"/>
+      <c r="B76" s="61">
+        <f t="shared" si="31"/>
         <v>67</v>
       </c>
       <c r="C76" s="52" t="s">
@@ -4708,8 +4697,8 @@
     </row>
     <row r="77" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="65">
-        <f>ROW(B77) - ROW($B$9)</f>
+      <c r="B77" s="61">
+        <f t="shared" si="31"/>
         <v>68</v>
       </c>
       <c r="C77" s="50" t="s">
@@ -4744,8 +4733,8 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="60">
-        <f t="shared" si="0"/>
+      <c r="B78" s="61">
+        <f t="shared" si="31"/>
         <v>69</v>
       </c>
       <c r="C78" s="52" t="s">
@@ -4780,8 +4769,8 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="65">
-        <f>ROW(B79) - ROW($B$9)</f>
+      <c r="B79" s="61">
+        <f t="shared" si="31"/>
         <v>70</v>
       </c>
       <c r="C79" s="50" t="s">
@@ -4816,8 +4805,8 @@
     </row>
     <row r="80" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="60">
-        <f t="shared" si="0"/>
+      <c r="B80" s="61">
+        <f t="shared" si="31"/>
         <v>71</v>
       </c>
       <c r="C80" s="52" t="s">
@@ -4852,63 +4841,63 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="60">
-        <f t="shared" si="0"/>
+      <c r="B81" s="61">
+        <f t="shared" si="31"/>
         <v>72</v>
       </c>
-      <c r="C81" s="61" t="s">
+      <c r="C81" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="D81" s="58" t="s">
         <v>349</v>
       </c>
-      <c r="D81" s="62" t="s">
+      <c r="E81" s="59" t="s">
         <v>350</v>
       </c>
-      <c r="E81" s="63" t="s">
+      <c r="F81" s="59" t="s">
+        <v>333</v>
+      </c>
+      <c r="G81" s="59" t="s">
         <v>351</v>
       </c>
-      <c r="F81" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="G81" s="63" t="s">
+      <c r="H81" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="H81" s="63" t="s">
-        <v>353</v>
-      </c>
-      <c r="I81" s="63" t="s">
+      <c r="I81" s="59" t="s">
         <v>336</v>
       </c>
-      <c r="J81" s="63">
+      <c r="J81" s="59">
         <v>1</v>
       </c>
-      <c r="K81" s="63">
+      <c r="K81" s="59">
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L81" s="63"/>
+      <c r="L81" s="59"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="B82" s="60">
-        <f t="shared" ref="B82:B83" si="35">ROW(B82) - ROW($B$9)</f>
+      <c r="B82" s="61">
+        <f t="shared" si="31"/>
         <v>73</v>
       </c>
       <c r="C82" s="52" t="s">
+        <v>348</v>
+      </c>
+      <c r="D82" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="D82" s="64" t="s">
-        <v>350</v>
-      </c>
       <c r="E82" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F82" s="36" t="s">
         <v>333</v>
       </c>
       <c r="G82" s="36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H82" s="36" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I82" s="36" t="s">
         <v>336</v>
@@ -4924,39 +4913,39 @@
     </row>
     <row r="83" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
-      <c r="B83" s="70">
-        <f t="shared" si="35"/>
+      <c r="B83" s="61">
+        <f t="shared" si="31"/>
         <v>74</v>
       </c>
-      <c r="C83" s="71" t="s">
+      <c r="C83" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D83" s="67" t="s">
         <v>349</v>
       </c>
-      <c r="D83" s="72" t="s">
-        <v>350</v>
-      </c>
-      <c r="E83" s="68" t="s">
+      <c r="E83" s="64" t="s">
+        <v>355</v>
+      </c>
+      <c r="F83" s="64" t="s">
+        <v>333</v>
+      </c>
+      <c r="G83" s="64" t="s">
         <v>356</v>
       </c>
-      <c r="F83" s="68" t="s">
-        <v>333</v>
-      </c>
-      <c r="G83" s="68" t="s">
-        <v>357</v>
-      </c>
-      <c r="H83" s="68" t="s">
-        <v>353</v>
-      </c>
-      <c r="I83" s="68" t="s">
+      <c r="H83" s="64" t="s">
+        <v>352</v>
+      </c>
+      <c r="I83" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="J83" s="68">
+      <c r="J83" s="64">
         <v>1</v>
       </c>
-      <c r="K83" s="68">
+      <c r="K83" s="64">
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L83" s="68"/>
+      <c r="L83" s="64"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
@@ -4970,7 +4959,7 @@
       <c r="I84" s="35"/>
       <c r="J84" s="35"/>
       <c r="K84" s="35"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="68"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="24"/>
@@ -4983,7 +4972,7 @@
       <c r="I85" s="9"/>
       <c r="J85" s="9"/>
       <c r="K85" s="9"/>
-      <c r="L85" s="69"/>
+      <c r="L85" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BOM/Client-BOM.xlsx
+++ b/BOM/Client-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C35280-50FE-49E7-BDC2-AE55C7835570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8AEF1D-59FA-433D-8AD0-8F7A2DB7E0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="367">
   <si>
     <t>Component list</t>
   </si>
@@ -289,9 +289,6 @@
     <t>U4, U5, U6, U7</t>
   </si>
   <si>
-    <t>U8, U9</t>
-  </si>
-  <si>
     <t>U10</t>
   </si>
   <si>
@@ -1109,6 +1106,21 @@
   </si>
   <si>
     <t>CC0402JRNPO8BN330</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>IC TRANSLTR BIDIRECTIONAL 8VSSOP</t>
+  </si>
+  <si>
+    <t>8-VSSOP</t>
+  </si>
+  <si>
+    <t>TXS0102DCUR</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1306,12 +1318,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF03A4CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1547,7 +1553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1612,10 +1618,10 @@
     <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1634,9 +1640,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1663,7 +1666,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1684,21 +1687,12 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1708,10 +1702,7 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1741,18 +1732,6 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1761,6 +1740,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2103,7 +2085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2113,7 +2095,7 @@
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="29.42578125" customWidth="1"/>
@@ -2128,74 +2110,74 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="38"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="46" t="s">
-        <v>346</v>
+      <c r="F2" s="45" t="s">
+        <v>345</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="37"/>
+      <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="39"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="47" t="s">
-        <v>347</v>
+      <c r="F3" s="46" t="s">
+        <v>346</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="76"/>
+      <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="39"/>
+      <c r="C4" s="38"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="48" t="s">
-        <v>347</v>
+      <c r="F4" s="47" t="s">
+        <v>346</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="77"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="39"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="48" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="14"/>
@@ -2203,12 +2185,12 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="77"/>
+      <c r="L5" s="68"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="40"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -2217,12 +2199,12 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="77"/>
+      <c r="L6" s="68"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="41"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -2231,12 +2213,12 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="77"/>
+      <c r="L7" s="68"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -2245,7 +2227,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="77"/>
+      <c r="L8" s="68"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2259,2720 +2241,2755 @@
         <v>25</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="I9" s="45" t="s">
-        <v>342</v>
+        <v>263</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>341</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="K9" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="K9" s="51" t="s">
+        <v>343</v>
+      </c>
+      <c r="L9" s="29" t="s">
         <v>344</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="61">
+      <c r="B10" s="56">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="73" t="s">
+      <c r="D10" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="71" t="s">
-        <v>166</v>
-      </c>
-      <c r="G10" s="71" t="s">
-        <v>208</v>
-      </c>
-      <c r="H10" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="I10" s="71" t="s">
-        <v>300</v>
-      </c>
-      <c r="J10" s="71">
+      <c r="E10" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="G10" s="69" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="I10" s="69" t="s">
+        <v>299</v>
+      </c>
+      <c r="J10" s="69">
         <v>1</v>
       </c>
-      <c r="K10" s="71">
+      <c r="K10" s="69">
         <f>J10*5</f>
         <v>5</v>
       </c>
-      <c r="L10" s="71"/>
+      <c r="L10" s="69"/>
     </row>
     <row r="11" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="61">
+      <c r="B11" s="56">
         <f t="shared" ref="B11:B74" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G11" s="69" t="s">
-        <v>339</v>
-      </c>
-      <c r="H11" s="59" t="s">
-        <v>265</v>
-      </c>
-      <c r="I11" s="59" t="s">
-        <v>301</v>
-      </c>
-      <c r="J11" s="59">
+      <c r="E11" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="H11" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I11" s="55" t="s">
+        <v>300</v>
+      </c>
+      <c r="J11" s="55">
         <v>28</v>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="55">
         <f t="shared" ref="K11" si="1">J11*5</f>
         <v>140</v>
       </c>
-      <c r="L11" s="59"/>
+      <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="61">
+      <c r="B12" s="56">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="73" t="s">
-        <v>332</v>
-      </c>
-      <c r="F12" s="73" t="s">
-        <v>167</v>
-      </c>
-      <c r="G12" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="H12" s="73" t="s">
-        <v>340</v>
-      </c>
-      <c r="I12" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="J12" s="73">
+      <c r="E12" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="I12" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="J12" s="50">
         <v>2</v>
       </c>
-      <c r="K12" s="73">
+      <c r="K12" s="50">
         <f>J12*5</f>
         <v>10</v>
       </c>
-      <c r="L12" s="74"/>
+      <c r="L12" s="52"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="61">
+      <c r="B13" s="56">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="69" t="s">
-        <v>357</v>
-      </c>
-      <c r="E13" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="59" t="s">
-        <v>333</v>
-      </c>
-      <c r="G13" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" s="59" t="s">
-        <v>266</v>
-      </c>
-      <c r="I13" s="59" t="s">
-        <v>303</v>
-      </c>
-      <c r="J13" s="59">
+      <c r="D13" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="E13" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G13" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="I13" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="J13" s="55">
         <v>3</v>
       </c>
-      <c r="K13" s="59">
+      <c r="K13" s="55">
         <f t="shared" ref="K13:K14" si="2">J13*5</f>
         <v>15</v>
       </c>
-      <c r="L13" s="70"/>
+      <c r="L13" s="65"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="61">
+      <c r="B14" s="56">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="73" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="73" t="s">
-        <v>169</v>
-      </c>
-      <c r="G14" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="H14" s="73" t="s">
-        <v>266</v>
-      </c>
-      <c r="I14" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="J14" s="73">
+      <c r="E14" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="H14" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="I14" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="J14" s="50">
         <v>1</v>
       </c>
-      <c r="K14" s="73">
+      <c r="K14" s="50">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L14" s="74"/>
+      <c r="L14" s="52"/>
     </row>
     <row r="15" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="61">
+      <c r="B15" s="56">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="59" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G15" s="59" t="s">
-        <v>211</v>
-      </c>
-      <c r="H15" s="59" t="s">
-        <v>265</v>
-      </c>
-      <c r="I15" s="59" t="s">
-        <v>305</v>
-      </c>
-      <c r="J15" s="59">
+      <c r="E15" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="H15" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I15" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="J15" s="55">
         <v>12</v>
       </c>
-      <c r="K15" s="59">
+      <c r="K15" s="55">
         <f>J15*5</f>
         <v>60</v>
       </c>
-      <c r="L15" s="59"/>
+      <c r="L15" s="55"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="61">
+      <c r="B16" s="56">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="73" t="s">
+      <c r="D16" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="73" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="73" t="s">
-        <v>212</v>
-      </c>
-      <c r="H16" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="I16" s="73" t="s">
-        <v>306</v>
-      </c>
-      <c r="J16" s="73">
+      <c r="E16" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="J16" s="50">
         <v>1</v>
       </c>
-      <c r="K16" s="73">
+      <c r="K16" s="50">
         <f t="shared" ref="K16" si="3">J16*5</f>
         <v>5</v>
       </c>
-      <c r="L16" s="74"/>
+      <c r="L16" s="52"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="61">
+      <c r="B17" s="56">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="59" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>362</v>
-      </c>
-      <c r="H17" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="I17" s="59" t="s">
-        <v>307</v>
-      </c>
-      <c r="J17" s="59">
+      <c r="E17" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="H17" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="J17" s="55">
         <v>1</v>
       </c>
-      <c r="K17" s="59">
+      <c r="K17" s="55">
         <f>J17*5</f>
         <v>5</v>
       </c>
-      <c r="L17" s="59"/>
+      <c r="L17" s="55"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="61">
+      <c r="B18" s="56">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="73" t="s">
+      <c r="D18" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="73" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="G18" s="73" t="s">
-        <v>213</v>
-      </c>
-      <c r="H18" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="I18" s="73" t="s">
-        <v>308</v>
-      </c>
-      <c r="J18" s="73">
+      <c r="E18" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I18" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="J18" s="50">
         <v>2</v>
       </c>
-      <c r="K18" s="73">
+      <c r="K18" s="50">
         <f t="shared" ref="K18" si="4">J18*5</f>
         <v>10</v>
       </c>
-      <c r="L18" s="74"/>
+      <c r="L18" s="52"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="61">
+      <c r="B19" s="56">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="H19" s="59" t="s">
-        <v>265</v>
-      </c>
-      <c r="I19" s="59" t="s">
-        <v>309</v>
-      </c>
-      <c r="J19" s="59">
+      <c r="E19" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="H19" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I19" s="55" t="s">
+        <v>308</v>
+      </c>
+      <c r="J19" s="55">
         <v>2</v>
       </c>
-      <c r="K19" s="59">
+      <c r="K19" s="55">
         <f>J19*5</f>
         <v>10</v>
       </c>
-      <c r="L19" s="59"/>
+      <c r="L19" s="55"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="61">
+      <c r="B20" s="56">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="E20" s="69" t="s">
         <v>358</v>
       </c>
-      <c r="E20" s="71" t="s">
+      <c r="F20" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="G20" s="69" t="s">
         <v>359</v>
       </c>
-      <c r="F20" s="71" t="s">
-        <v>333</v>
-      </c>
-      <c r="G20" s="71" t="s">
+      <c r="H20" s="69" t="s">
+        <v>265</v>
+      </c>
+      <c r="I20" s="69" t="s">
         <v>360</v>
       </c>
-      <c r="H20" s="71" t="s">
-        <v>266</v>
-      </c>
-      <c r="I20" s="71" t="s">
-        <v>361</v>
-      </c>
-      <c r="J20" s="71">
+      <c r="J20" s="69">
         <v>1</v>
       </c>
-      <c r="K20" s="71">
+      <c r="K20" s="69">
         <f>J20*5</f>
         <v>5</v>
       </c>
-      <c r="L20" s="71"/>
+      <c r="L20" s="69"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="61">
+      <c r="B21" s="56">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="G21" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="H21" s="51" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J21" s="51">
+      <c r="E21" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J21" s="50">
         <v>7</v>
       </c>
-      <c r="K21" s="51">
+      <c r="K21" s="50">
         <f t="shared" ref="K21" si="5">J21*5</f>
         <v>35</v>
       </c>
-      <c r="L21" s="55"/>
+      <c r="L21" s="52"/>
     </row>
     <row r="22" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="61">
+      <c r="B22" s="56">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J22" s="36">
+      <c r="E22" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="H22" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="I22" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J22" s="55">
         <v>2</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="55">
         <f>J22*5</f>
         <v>10</v>
       </c>
-      <c r="L22" s="36"/>
+      <c r="L22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="61">
+      <c r="B23" s="56">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J23" s="51">
+      <c r="E23" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="I23" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J23" s="50">
         <v>1</v>
       </c>
-      <c r="K23" s="51">
+      <c r="K23" s="50">
         <f t="shared" ref="K23" si="6">J23*5</f>
         <v>5</v>
       </c>
-      <c r="L23" s="55"/>
+      <c r="L23" s="52"/>
     </row>
     <row r="24" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="61">
+      <c r="B24" s="56">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>341</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J24" s="36">
+      <c r="E24" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="G24" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="H24" s="55" t="s">
+        <v>340</v>
+      </c>
+      <c r="I24" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J24" s="55">
         <v>1</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="55">
         <f>J24*5</f>
         <v>5</v>
       </c>
-      <c r="L24" s="36"/>
+      <c r="L24" s="55"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="61">
+      <c r="B25" s="56">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="H25" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="I25" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J25" s="51">
+      <c r="E25" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="I25" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J25" s="50">
         <v>8</v>
       </c>
-      <c r="K25" s="51">
+      <c r="K25" s="50">
         <f t="shared" ref="K25" si="7">J25*5</f>
         <v>40</v>
       </c>
-      <c r="L25" s="55"/>
+      <c r="L25" s="52"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="61">
+      <c r="B26" s="56">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="G26" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J26" s="36">
+      <c r="E26" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="H26" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="I26" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J26" s="55">
         <v>1</v>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="55">
         <f>J26*5</f>
         <v>5</v>
       </c>
-      <c r="L26" s="36"/>
+      <c r="L26" s="55"/>
     </row>
     <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="61">
+      <c r="B27" s="56">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="H27" s="51" t="s">
-        <v>273</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J27" s="51">
+      <c r="E27" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="H27" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="I27" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J27" s="50">
         <v>3</v>
       </c>
-      <c r="K27" s="51">
+      <c r="K27" s="50">
         <f t="shared" ref="K27" si="8">J27*5</f>
         <v>15</v>
       </c>
-      <c r="L27" s="55"/>
+      <c r="L27" s="52"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="61">
+      <c r="B28" s="56">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="H28" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="I28" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J28" s="36">
+      <c r="E28" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="H28" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="I28" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J28" s="55">
         <v>1</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="55">
         <f>J28*5</f>
         <v>5</v>
       </c>
-      <c r="L28" s="36"/>
+      <c r="L28" s="55"/>
     </row>
     <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="61">
+      <c r="B29" s="56">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="H29" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="I29" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J29" s="51">
+      <c r="E29" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>268</v>
+      </c>
+      <c r="I29" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J29" s="50">
         <v>5</v>
       </c>
-      <c r="K29" s="51">
+      <c r="K29" s="50">
         <f t="shared" ref="K29" si="9">J29*5</f>
         <v>25</v>
       </c>
-      <c r="L29" s="55"/>
+      <c r="L29" s="52"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="61">
+      <c r="B30" s="56">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>178</v>
-      </c>
-      <c r="G30" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="H30" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="I30" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J30" s="36">
+      <c r="E30" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="G30" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="H30" s="55" t="s">
+        <v>274</v>
+      </c>
+      <c r="I30" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J30" s="55">
         <v>1</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="55">
         <f>J30*5</f>
         <v>5</v>
       </c>
-      <c r="L30" s="36"/>
+      <c r="L30" s="55"/>
     </row>
     <row r="31" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="61">
+      <c r="B31" s="56">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="51" t="s">
+      <c r="D31" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="H31" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="I31" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J31" s="51">
+      <c r="E31" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="H31" s="50" t="s">
+        <v>275</v>
+      </c>
+      <c r="I31" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J31" s="50">
         <v>2</v>
       </c>
-      <c r="K31" s="51">
+      <c r="K31" s="50">
         <f t="shared" ref="K31" si="10">J31*5</f>
         <v>10</v>
       </c>
-      <c r="L31" s="55"/>
+      <c r="L31" s="52"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="61">
+      <c r="B32" s="56">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="G32" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="H32" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="I32" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="J32" s="36">
+      <c r="E32" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="G32" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="H32" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="I32" s="55" t="s">
+        <v>309</v>
+      </c>
+      <c r="J32" s="55">
         <v>1</v>
       </c>
-      <c r="K32" s="36">
+      <c r="K32" s="55">
         <f>J32*5</f>
         <v>5</v>
       </c>
-      <c r="L32" s="36"/>
+      <c r="L32" s="55"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="61">
+      <c r="B33" s="56">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="51" t="s">
+      <c r="D33" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="F33" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="G33" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="H33" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="I33" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J33" s="51">
+      <c r="E33" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J33" s="50">
         <v>8</v>
       </c>
-      <c r="K33" s="51">
+      <c r="K33" s="50">
         <f t="shared" ref="K33" si="11">J33*5</f>
         <v>40</v>
       </c>
-      <c r="L33" s="55"/>
+      <c r="L33" s="52"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="61">
+      <c r="B34" s="56">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="G34" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="H34" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="I34" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J34" s="36">
+      <c r="E34" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G34" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="H34" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="I34" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J34" s="55">
         <v>2</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="55">
         <f>J34*5</f>
         <v>10</v>
       </c>
-      <c r="L34" s="36"/>
+      <c r="L34" s="55"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="61">
+      <c r="B35" s="56">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="F35" s="51">
+      <c r="E35" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="50">
         <v>1051330011</v>
       </c>
-      <c r="G35" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J35" s="51">
+      <c r="G35" s="50" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>278</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J35" s="50">
         <v>1</v>
       </c>
-      <c r="K35" s="51">
+      <c r="K35" s="50">
         <f t="shared" ref="K35:K36" si="12">J35*5</f>
         <v>5</v>
       </c>
-      <c r="L35" s="55"/>
+      <c r="L35" s="52"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="61">
+      <c r="B36" s="56">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="52" t="s">
+      <c r="C36" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="F36" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="G36" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="H36" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="I36" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J36" s="36">
+      <c r="E36" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G36" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="H36" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="I36" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J36" s="55">
         <v>6</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="55">
         <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="L36" s="56"/>
+      <c r="L36" s="65"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="61">
+      <c r="B37" s="56">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="I37" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="D37" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="F37" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="H37" s="51" t="s">
-        <v>281</v>
-      </c>
-      <c r="I37" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J37" s="51">
+      <c r="J37" s="50">
         <v>2</v>
       </c>
-      <c r="K37" s="51">
+      <c r="K37" s="50">
         <f>J37*5</f>
         <v>10</v>
       </c>
-      <c r="L37" s="55"/>
+      <c r="L37" s="52"/>
     </row>
     <row r="38" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="61">
+      <c r="B38" s="56">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="G38" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="H38" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="I38" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J38" s="36">
+      <c r="E38" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G38" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="I38" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J38" s="55">
         <v>1</v>
       </c>
-      <c r="K38" s="36">
+      <c r="K38" s="55">
         <f t="shared" ref="K38" si="13">J38*5</f>
         <v>5</v>
       </c>
-      <c r="L38" s="36"/>
+      <c r="L38" s="55"/>
     </row>
     <row r="39" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="61">
+      <c r="B39" s="56">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="51" t="s">
+      <c r="D39" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="F39" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="H39" s="51" t="s">
-        <v>283</v>
-      </c>
-      <c r="I39" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J39" s="51">
+      <c r="E39" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="H39" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J39" s="50">
         <v>1</v>
       </c>
-      <c r="K39" s="51">
+      <c r="K39" s="50">
         <f>J39*5</f>
         <v>5</v>
       </c>
-      <c r="L39" s="55"/>
+      <c r="L39" s="52"/>
     </row>
     <row r="40" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="61">
+      <c r="B40" s="56">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="52" t="s">
+      <c r="C40" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="G40" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="H40" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J40" s="36">
+      <c r="E40" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G40" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="H40" s="55" t="s">
+        <v>282</v>
+      </c>
+      <c r="I40" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J40" s="55">
         <v>1</v>
       </c>
-      <c r="K40" s="36">
+      <c r="K40" s="55">
         <f t="shared" ref="K40" si="14">J40*5</f>
         <v>5</v>
       </c>
-      <c r="L40" s="36"/>
+      <c r="L40" s="55"/>
     </row>
     <row r="41" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="61">
+      <c r="B41" s="56">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="51" t="s">
+      <c r="D41" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="H41" s="51" t="s">
-        <v>281</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J41" s="51">
+      <c r="E41" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="G41" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="H41" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="I41" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J41" s="50">
         <v>1</v>
       </c>
-      <c r="K41" s="51">
+      <c r="K41" s="50">
         <f>J41*5</f>
         <v>5</v>
       </c>
-      <c r="L41" s="55"/>
+      <c r="L41" s="52"/>
     </row>
     <row r="42" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="61">
+      <c r="B42" s="56">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="D42" s="53" t="s">
+      <c r="D42" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="G42" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="H42" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="I42" s="36" t="s">
-        <v>311</v>
-      </c>
-      <c r="J42" s="36">
+      <c r="E42" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G42" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="H42" s="55" t="s">
+        <v>283</v>
+      </c>
+      <c r="I42" s="55" t="s">
+        <v>310</v>
+      </c>
+      <c r="J42" s="55">
         <v>1</v>
       </c>
-      <c r="K42" s="36">
+      <c r="K42" s="55">
         <f t="shared" ref="K42" si="15">J42*5</f>
         <v>5</v>
       </c>
-      <c r="L42" s="36"/>
+      <c r="L42" s="55"/>
     </row>
     <row r="43" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="61">
+      <c r="B43" s="56">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="51" t="s">
+      <c r="D43" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="F43" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="H43" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="I43" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="J43" s="51">
+      <c r="E43" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="F43" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="G43" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="H43" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="J43" s="50">
         <v>1</v>
       </c>
-      <c r="K43" s="51">
+      <c r="K43" s="50">
         <f>J43*5</f>
         <v>5</v>
       </c>
-      <c r="L43" s="55"/>
+      <c r="L43" s="52"/>
     </row>
     <row r="44" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="61">
+      <c r="B44" s="56">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="52" t="s">
+      <c r="C44" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="53" t="s">
+      <c r="D44" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="G44" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="H44" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="I44" s="36" t="s">
-        <v>312</v>
-      </c>
-      <c r="J44" s="36">
+      <c r="E44" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="F44" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="G44" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="H44" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="I44" s="55" t="s">
+        <v>311</v>
+      </c>
+      <c r="J44" s="55">
         <v>1</v>
       </c>
-      <c r="K44" s="36">
+      <c r="K44" s="55">
         <f t="shared" ref="K44:K45" si="16">J44*5</f>
         <v>5</v>
       </c>
-      <c r="L44" s="36"/>
+      <c r="L44" s="55"/>
     </row>
     <row r="45" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="61">
+      <c r="B45" s="56">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="51" t="s">
+      <c r="D45" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="E45" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="F45" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="H45" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I45" s="51" t="s">
-        <v>313</v>
-      </c>
-      <c r="J45" s="51">
+      <c r="E45" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="G45" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="H45" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="I45" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="J45" s="50">
         <v>3</v>
       </c>
-      <c r="K45" s="51">
+      <c r="K45" s="50">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
-      <c r="L45" s="55"/>
+      <c r="L45" s="52"/>
     </row>
     <row r="46" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="61">
+      <c r="B46" s="56">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="53" t="s">
+      <c r="D46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="G46" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="H46" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="I46" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J46" s="36">
+      <c r="E46" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="G46" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="I46" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J46" s="55">
         <v>4</v>
       </c>
-      <c r="K46" s="36">
+      <c r="K46" s="55">
         <f>J46*5</f>
         <v>20</v>
       </c>
-      <c r="L46" s="36"/>
+      <c r="L46" s="55"/>
     </row>
     <row r="47" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="61">
+      <c r="B47" s="56">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="51" t="s">
+      <c r="D47" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="E47" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="F47" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="G47" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="H47" s="51" t="s">
-        <v>287</v>
-      </c>
-      <c r="I47" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J47" s="51">
+      <c r="E47" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="H47" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J47" s="50">
         <v>1</v>
       </c>
-      <c r="K47" s="51">
+      <c r="K47" s="50">
         <f t="shared" ref="K47:K48" si="17">J47*5</f>
         <v>5</v>
       </c>
-      <c r="L47" s="55"/>
+      <c r="L47" s="52"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="61">
+      <c r="B48" s="56">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="52" t="s">
+      <c r="C48" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="53" t="s">
+      <c r="D48" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="G48" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="H48" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="I48" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J48" s="36">
+      <c r="E48" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="F48" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="G48" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="H48" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="I48" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J48" s="55">
         <v>1</v>
       </c>
-      <c r="K48" s="36">
+      <c r="K48" s="55">
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L48" s="36"/>
+      <c r="L48" s="55"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="61">
+      <c r="B49" s="56">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="62" t="s">
-        <v>314</v>
-      </c>
-      <c r="D49" s="63" t="s">
+      <c r="C49" s="57" t="s">
+        <v>313</v>
+      </c>
+      <c r="D49" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="E49" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="F49" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="G49" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="H49" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="I49" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="J49" s="63">
+      <c r="E49" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G49" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="H49" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="I49" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="J49" s="58">
         <v>6</v>
       </c>
-      <c r="K49" s="63">
+      <c r="K49" s="58">
         <f>J49*5</f>
         <v>30</v>
       </c>
-      <c r="L49" s="63"/>
+      <c r="L49" s="58"/>
     </row>
     <row r="50" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="61">
+      <c r="B50" s="56">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="52" t="s">
+      <c r="C50" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D50" s="53" t="s">
+      <c r="D50" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="E50" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F50" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="G50" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="H50" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="I50" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J50" s="36">
+      <c r="E50" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="F50" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="G50" s="55" t="s">
+        <v>234</v>
+      </c>
+      <c r="H50" s="55" t="s">
+        <v>288</v>
+      </c>
+      <c r="I50" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J50" s="55">
         <v>4</v>
       </c>
-      <c r="K50" s="36">
+      <c r="K50" s="55">
         <f t="shared" ref="K50" si="18">J50*5</f>
         <v>20</v>
       </c>
-      <c r="L50" s="36"/>
+      <c r="L50" s="55"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="61">
+      <c r="B51" s="56">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="50" t="s">
+      <c r="C51" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="51" t="s">
+      <c r="D51" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="H51" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I51" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="J51" s="51">
+      <c r="E51" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G51" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="H51" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I51" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="J51" s="50">
         <v>1</v>
       </c>
-      <c r="K51" s="51">
+      <c r="K51" s="50">
         <f>J51*5</f>
         <v>5</v>
       </c>
-      <c r="L51" s="55"/>
+      <c r="L51" s="52"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="61">
+      <c r="B52" s="56">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="52" t="s">
+      <c r="C52" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="53" t="s">
+      <c r="D52" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="E52" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="F52" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G52" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="H52" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I52" s="36" t="s">
-        <v>343</v>
-      </c>
-      <c r="J52" s="36">
+      <c r="E52" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="F52" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G52" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H52" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I52" s="55" t="s">
+        <v>342</v>
+      </c>
+      <c r="J52" s="55">
         <v>1</v>
       </c>
-      <c r="K52" s="36">
+      <c r="K52" s="55">
         <f t="shared" ref="K52" si="19">J52*5</f>
         <v>5</v>
       </c>
-      <c r="L52" s="36"/>
+      <c r="L52" s="55"/>
     </row>
     <row r="53" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="61">
+      <c r="B53" s="56">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="51" t="s">
+      <c r="D53" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E53" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="F53" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>238</v>
-      </c>
-      <c r="H53" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I53" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="J53" s="51">
+      <c r="E53" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F53" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="H53" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>315</v>
+      </c>
+      <c r="J53" s="50">
         <v>13</v>
       </c>
-      <c r="K53" s="51">
+      <c r="K53" s="50">
         <f>J53*5</f>
         <v>65</v>
       </c>
-      <c r="L53" s="55"/>
+      <c r="L53" s="52"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="61">
+      <c r="B54" s="56">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="52" t="s">
+      <c r="C54" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="53" t="s">
+      <c r="D54" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="E54" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="F54" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G54" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="H54" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I54" s="36" t="s">
-        <v>317</v>
-      </c>
-      <c r="J54" s="36">
+      <c r="E54" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="F54" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G54" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="H54" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I54" s="55" t="s">
+        <v>316</v>
+      </c>
+      <c r="J54" s="55">
         <v>1</v>
       </c>
-      <c r="K54" s="36">
+      <c r="K54" s="55">
         <f t="shared" ref="K54" si="20">J54*5</f>
         <v>5</v>
       </c>
-      <c r="L54" s="36"/>
+      <c r="L54" s="55"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="61">
+      <c r="B55" s="56">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="51" t="s">
+      <c r="D55" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="F55" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G55" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="H55" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I55" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="J55" s="51">
+      <c r="E55" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="F55" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G55" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="H55" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I55" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="J55" s="50">
         <v>1</v>
       </c>
-      <c r="K55" s="51">
+      <c r="K55" s="50">
         <f>J55*5</f>
         <v>5</v>
       </c>
-      <c r="L55" s="55"/>
+      <c r="L55" s="52"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="61">
+      <c r="B56" s="56">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="52" t="s">
+      <c r="C56" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="53" t="s">
+      <c r="D56" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="E56" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G56" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="H56" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>319</v>
-      </c>
-      <c r="J56" s="36">
+      <c r="E56" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="F56" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G56" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="H56" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I56" s="55" t="s">
+        <v>318</v>
+      </c>
+      <c r="J56" s="55">
         <v>2</v>
       </c>
-      <c r="K56" s="36">
+      <c r="K56" s="55">
         <f t="shared" ref="K56" si="21">J56*5</f>
         <v>10</v>
       </c>
-      <c r="L56" s="36"/>
+      <c r="L56" s="55"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="61">
+      <c r="B57" s="56">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="51" t="s">
+      <c r="D57" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="F57" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="H57" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I57" s="51" t="s">
-        <v>320</v>
-      </c>
-      <c r="J57" s="51">
+      <c r="E57" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G57" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="H57" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I57" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="J57" s="50">
         <v>3</v>
       </c>
-      <c r="K57" s="51">
+      <c r="K57" s="50">
         <f>J57*5</f>
         <v>15</v>
       </c>
-      <c r="L57" s="55"/>
+      <c r="L57" s="52"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="61">
+      <c r="B58" s="56">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="52" t="s">
+      <c r="C58" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="53" t="s">
+      <c r="D58" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="E58" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G58" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="H58" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I58" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="J58" s="36">
+      <c r="E58" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F58" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G58" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="H58" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I58" s="55" t="s">
+        <v>320</v>
+      </c>
+      <c r="J58" s="55">
         <v>4</v>
       </c>
-      <c r="K58" s="36">
+      <c r="K58" s="55">
         <f t="shared" ref="K58" si="22">J58*5</f>
         <v>20</v>
       </c>
-      <c r="L58" s="36"/>
+      <c r="L58" s="55"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="61">
+      <c r="B59" s="56">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="C59" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="51" t="s">
+      <c r="D59" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="E59" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="F59" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G59" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="H59" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I59" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="J59" s="51">
+      <c r="E59" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="F59" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G59" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="H59" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I59" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="J59" s="50">
         <v>1</v>
       </c>
-      <c r="K59" s="51">
+      <c r="K59" s="50">
         <f>J59*5</f>
         <v>5</v>
       </c>
-      <c r="L59" s="55"/>
+      <c r="L59" s="52"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="61">
+      <c r="B60" s="56">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="52" t="s">
+      <c r="C60" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="53" t="s">
+      <c r="D60" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="E60" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="F60" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G60" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="H60" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I60" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="J60" s="36">
+      <c r="E60" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="F60" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G60" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="H60" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I60" s="55" t="s">
+        <v>322</v>
+      </c>
+      <c r="J60" s="55">
         <v>3</v>
       </c>
-      <c r="K60" s="36">
+      <c r="K60" s="55">
         <f t="shared" ref="K60" si="23">J60*5</f>
         <v>15</v>
       </c>
-      <c r="L60" s="36"/>
+      <c r="L60" s="55"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="61">
+      <c r="B61" s="56">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="50" t="s">
+      <c r="C61" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="51" t="s">
+      <c r="D61" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="E61" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="F61" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="H61" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I61" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="J61" s="51">
+      <c r="E61" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F61" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G61" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="H61" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I61" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="J61" s="50">
         <v>6</v>
       </c>
-      <c r="K61" s="51">
+      <c r="K61" s="50">
         <f>J61*5</f>
         <v>30</v>
       </c>
-      <c r="L61" s="55"/>
+      <c r="L61" s="52"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="61">
+      <c r="B62" s="56">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="52" t="s">
+      <c r="C62" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="53" t="s">
+      <c r="D62" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="F62" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G62" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="H62" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I62" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="J62" s="36">
+      <c r="E62" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="F62" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G62" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="H62" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I62" s="55" t="s">
+        <v>324</v>
+      </c>
+      <c r="J62" s="55">
         <v>4</v>
       </c>
-      <c r="K62" s="36">
+      <c r="K62" s="55">
         <f t="shared" ref="K62" si="24">J62*5</f>
         <v>20</v>
       </c>
-      <c r="L62" s="36"/>
+      <c r="L62" s="55"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="61">
+      <c r="B63" s="56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="51" t="s">
+      <c r="D63" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E63" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="F63" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G63" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="H63" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I63" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="J63" s="51">
+      <c r="E63" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>247</v>
+      </c>
+      <c r="H63" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="J63" s="50">
         <v>1</v>
       </c>
-      <c r="K63" s="51">
+      <c r="K63" s="50">
         <f>J63*5</f>
         <v>5</v>
       </c>
-      <c r="L63" s="55"/>
+      <c r="L63" s="52"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="61">
+      <c r="B64" s="56">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="52" t="s">
+      <c r="C64" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="53" t="s">
+      <c r="D64" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="E64" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="F64" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G64" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="H64" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I64" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="J64" s="36">
+      <c r="E64" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G64" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="H64" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I64" s="55" t="s">
+        <v>326</v>
+      </c>
+      <c r="J64" s="55">
         <v>3</v>
       </c>
-      <c r="K64" s="36">
+      <c r="K64" s="55">
         <f t="shared" ref="K64" si="25">J64*5</f>
         <v>15</v>
       </c>
-      <c r="L64" s="36"/>
+      <c r="L64" s="55"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="61">
+      <c r="B65" s="56">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="50" t="s">
+      <c r="C65" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="51" t="s">
+      <c r="D65" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="E65" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="F65" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="H65" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I65" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="J65" s="51">
+      <c r="E65" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="H65" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I65" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="J65" s="50">
         <v>1</v>
       </c>
-      <c r="K65" s="51">
+      <c r="K65" s="50">
         <f>J65*5</f>
         <v>5</v>
       </c>
-      <c r="L65" s="55"/>
+      <c r="L65" s="52"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="61">
+      <c r="B66" s="56">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="52" t="s">
+      <c r="C66" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="53" t="s">
+      <c r="D66" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="E66" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="F66" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="G66" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="H66" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I66" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="J66" s="36">
+      <c r="E66" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="F66" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="G66" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="H66" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I66" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="J66" s="55">
         <v>1</v>
       </c>
-      <c r="K66" s="36">
+      <c r="K66" s="55">
         <f t="shared" ref="K66" si="26">J66*5</f>
         <v>5</v>
       </c>
-      <c r="L66" s="36"/>
+      <c r="L66" s="55"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="61">
+      <c r="B67" s="56">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="50" t="s">
+      <c r="C67" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="51" t="s">
+      <c r="D67" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="E67" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="F67" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="G67" s="51" t="s">
-        <v>252</v>
-      </c>
-      <c r="H67" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I67" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="J67" s="51">
+      <c r="E67" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="G67" s="50" t="s">
+        <v>251</v>
+      </c>
+      <c r="H67" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="I67" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="J67" s="50">
         <v>1</v>
       </c>
-      <c r="K67" s="51">
+      <c r="K67" s="50">
         <f>J67*5</f>
         <v>5</v>
       </c>
-      <c r="L67" s="55"/>
+      <c r="L67" s="52"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="61">
+      <c r="B68" s="56">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="52" t="s">
+      <c r="C68" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D68" s="53" t="s">
+      <c r="D68" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="E68" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="F68" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="G68" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="H68" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="I68" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="J68" s="36">
+      <c r="E68" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="F68" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="G68" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H68" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="I68" s="55" t="s">
+        <v>329</v>
+      </c>
+      <c r="J68" s="55">
         <v>1</v>
       </c>
-      <c r="K68" s="36">
+      <c r="K68" s="55">
         <f t="shared" ref="K68" si="27">J68*5</f>
         <v>5</v>
       </c>
-      <c r="L68" s="36"/>
+      <c r="L68" s="55"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="61">
+      <c r="B69" s="56">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="62" t="s">
-        <v>337</v>
-      </c>
-      <c r="D69" s="63" t="s">
+      <c r="C69" s="57" t="s">
+        <v>336</v>
+      </c>
+      <c r="D69" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="E69" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="F69" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="G69" s="63" t="s">
-        <v>197</v>
-      </c>
-      <c r="H69" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="I69" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="J69" s="63">
+      <c r="E69" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="F69" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="G69" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="I69" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="J69" s="58">
         <v>2</v>
       </c>
-      <c r="K69" s="63">
+      <c r="K69" s="58">
         <f>J69*5</f>
         <v>10</v>
       </c>
-      <c r="L69" s="63"/>
+      <c r="L69" s="58"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="61">
+      <c r="B70" s="56">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="52" t="s">
-        <v>338</v>
-      </c>
-      <c r="D70" s="53" t="s">
+      <c r="C70" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="D70" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="E70" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="F70" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="G70" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="H70" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="I70" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J70" s="36">
+      <c r="E70" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="F70" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="G70" s="55" t="s">
+        <v>253</v>
+      </c>
+      <c r="H70" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="I70" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J70" s="55">
         <v>1</v>
       </c>
-      <c r="K70" s="36">
+      <c r="K70" s="55">
         <f t="shared" ref="K70" si="28">J70*5</f>
         <v>5</v>
       </c>
-      <c r="L70" s="36"/>
+      <c r="L70" s="55"/>
     </row>
     <row r="71" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="61">
+      <c r="B71" s="56">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="50" t="s">
+      <c r="C71" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="51" t="s">
+      <c r="D71" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="E71" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="F71" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="G71" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="H71" s="51" t="s">
-        <v>291</v>
-      </c>
-      <c r="I71" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J71" s="51">
+      <c r="E71" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="F71" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="H71" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="I71" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J71" s="50">
         <v>1</v>
       </c>
-      <c r="K71" s="51">
+      <c r="K71" s="50">
         <f>J71*5</f>
         <v>5</v>
       </c>
-      <c r="L71" s="55"/>
+      <c r="L71" s="52"/>
     </row>
     <row r="72" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="61">
+      <c r="B72" s="56">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="52" t="s">
+      <c r="C72" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="53" t="s">
+      <c r="D72" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="E72" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="F72" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="G72" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="H72" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="I72" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J72" s="36">
+      <c r="E72" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="G72" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="H72" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="I72" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J72" s="55">
         <v>1</v>
       </c>
-      <c r="K72" s="36">
+      <c r="K72" s="55">
         <f t="shared" ref="K72" si="29">J72*5</f>
         <v>5</v>
       </c>
-      <c r="L72" s="36"/>
+      <c r="L72" s="55"/>
     </row>
     <row r="73" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="61">
+      <c r="B73" s="56">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="50" t="s">
+      <c r="C73" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="51" t="s">
+      <c r="D73" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="E73" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="F73" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="G73" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="H73" s="51" t="s">
-        <v>293</v>
-      </c>
-      <c r="I73" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J73" s="51">
+      <c r="E73" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="F73" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="G73" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="H73" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="I73" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J73" s="50">
         <v>1</v>
       </c>
-      <c r="K73" s="51">
+      <c r="K73" s="50">
         <f>J73*5</f>
         <v>5</v>
       </c>
-      <c r="L73" s="55"/>
+      <c r="L73" s="52"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="61">
+      <c r="B74" s="56">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="52" t="s">
+      <c r="C74" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="53" t="s">
+      <c r="D74" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="E74" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="F74" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="G74" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="H74" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="I74" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J74" s="36">
+      <c r="E74" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="F74" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="G74" s="55" t="s">
+        <v>257</v>
+      </c>
+      <c r="H74" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="I74" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J74" s="55">
         <v>4</v>
       </c>
-      <c r="K74" s="36">
+      <c r="K74" s="55">
         <f t="shared" ref="K74" si="30">J74*5</f>
         <v>20</v>
       </c>
-      <c r="L74" s="36"/>
+      <c r="L74" s="55"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="61">
-        <f t="shared" ref="B75:B83" si="31">ROW(B75) - ROW($B$9)</f>
+      <c r="B75" s="56">
+        <f t="shared" ref="B75:B84" si="31">ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="50" t="s">
+      <c r="C75" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D75" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E75" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="F75" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>259</v>
-      </c>
-      <c r="H75" s="51" t="s">
-        <v>295</v>
-      </c>
-      <c r="I75" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J75" s="51">
-        <v>2</v>
-      </c>
-      <c r="K75" s="51">
+      <c r="D75" s="50" t="s">
+        <v>363</v>
+      </c>
+      <c r="E75" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="F75" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="G75" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="H75" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="I75" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J75" s="50">
+        <v>1</v>
+      </c>
+      <c r="K75" s="50">
         <f>J75*5</f>
-        <v>10</v>
-      </c>
-      <c r="L75" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="L75" s="52"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="61">
-        <f t="shared" si="31"/>
+      <c r="B76" s="56">
         <v>67</v>
       </c>
-      <c r="C76" s="52" t="s">
+      <c r="C76" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D76" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="F76" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="G76" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="H76" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="I76" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J76" s="36">
+      <c r="D76" s="50" t="s">
+        <v>362</v>
+      </c>
+      <c r="E76" s="69" t="s">
+        <v>364</v>
+      </c>
+      <c r="F76" s="69" t="s">
+        <v>365</v>
+      </c>
+      <c r="G76" s="69" t="s">
+        <v>366</v>
+      </c>
+      <c r="H76" s="69" t="s">
+        <v>294</v>
+      </c>
+      <c r="I76" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J76" s="50">
         <v>1</v>
       </c>
-      <c r="K76" s="36">
-        <f t="shared" ref="K76" si="32">J76*5</f>
+      <c r="K76" s="50">
+        <f>J76*5</f>
         <v>5</v>
       </c>
-      <c r="L76" s="36"/>
-    </row>
-    <row r="77" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L76" s="52"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="61">
+      <c r="B77" s="56">
         <f t="shared" si="31"/>
         <v>68</v>
       </c>
-      <c r="C77" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D77" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="E77" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="F77" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="G77" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="H77" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="I77" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J77" s="51">
+      <c r="C77" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D77" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77" s="55" t="s">
+        <v>159</v>
+      </c>
+      <c r="F77" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="G77" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="H77" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="I77" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J77" s="55">
         <v>1</v>
       </c>
-      <c r="K77" s="51">
-        <f>J77*5</f>
+      <c r="K77" s="55">
+        <f t="shared" ref="K77" si="32">J77*5</f>
         <v>5</v>
       </c>
       <c r="L77" s="55"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="61">
+      <c r="B78" s="56">
         <f t="shared" si="31"/>
         <v>69</v>
       </c>
-      <c r="C78" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="E78" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="F78" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G78" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="H78" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="I78" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J78" s="36">
+      <c r="C78" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="F78" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="G78" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="H78" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="I78" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J78" s="50">
         <v>1</v>
       </c>
-      <c r="K78" s="36">
-        <f t="shared" ref="K78" si="33">J78*5</f>
+      <c r="K78" s="50">
+        <f>J78*5</f>
         <v>5</v>
       </c>
-      <c r="L78" s="36"/>
+      <c r="L78" s="52"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="61">
+      <c r="B79" s="56">
         <f t="shared" si="31"/>
         <v>70</v>
       </c>
-      <c r="C79" s="50" t="s">
+      <c r="C79" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D79" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="E79" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="F79" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="G79" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="H79" s="51" t="s">
-        <v>298</v>
-      </c>
-      <c r="I79" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="J79" s="51">
+      <c r="D79" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="E79" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="F79" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="G79" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="H79" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="I79" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J79" s="55">
         <v>1</v>
       </c>
-      <c r="K79" s="51">
-        <f>J79*5</f>
+      <c r="K79" s="55">
+        <f t="shared" ref="K79" si="33">J79*5</f>
         <v>5</v>
       </c>
       <c r="L79" s="55"/>
     </row>
-    <row r="80" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="61">
+      <c r="B80" s="56">
         <f t="shared" si="31"/>
         <v>71</v>
       </c>
-      <c r="C80" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="D80" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="E80" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="F80" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="G80" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H80" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="I80" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J80" s="36">
+      <c r="C80" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="F80" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="G80" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="H80" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="I80" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J80" s="50">
         <v>1</v>
       </c>
-      <c r="K80" s="36">
-        <f t="shared" ref="K80:K83" si="34">J80*5</f>
+      <c r="K80" s="50">
+        <f>J80*5</f>
         <v>5</v>
       </c>
-      <c r="L80" s="36"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L80" s="52"/>
+    </row>
+    <row r="81" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="61">
+      <c r="B81" s="56">
         <f t="shared" si="31"/>
         <v>72</v>
       </c>
-      <c r="C81" s="57" t="s">
+      <c r="C81" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="G81" s="55" t="s">
+        <v>262</v>
+      </c>
+      <c r="H81" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="I81" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J81" s="55">
+        <v>1</v>
+      </c>
+      <c r="K81" s="55">
+        <f t="shared" ref="K81:K84" si="34">J81*5</f>
+        <v>5</v>
+      </c>
+      <c r="L81" s="55"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="56">
+        <f t="shared" si="31"/>
+        <v>73</v>
+      </c>
+      <c r="C82" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D82" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="D81" s="58" t="s">
+      <c r="E82" s="55" t="s">
         <v>349</v>
       </c>
-      <c r="E81" s="59" t="s">
+      <c r="F82" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G82" s="55" t="s">
         <v>350</v>
       </c>
-      <c r="F81" s="59" t="s">
-        <v>333</v>
-      </c>
-      <c r="G81" s="59" t="s">
+      <c r="H82" s="55" t="s">
         <v>351</v>
       </c>
-      <c r="H81" s="59" t="s">
-        <v>352</v>
-      </c>
-      <c r="I81" s="59" t="s">
-        <v>336</v>
-      </c>
-      <c r="J81" s="59">
+      <c r="I82" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J82" s="55">
         <v>1</v>
       </c>
-      <c r="K81" s="59">
+      <c r="K82" s="55">
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L81" s="59"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="61">
+      <c r="L82" s="55"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="56">
         <f t="shared" si="31"/>
-        <v>73</v>
-      </c>
-      <c r="C82" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D83" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="D82" s="60" t="s">
-        <v>349</v>
-      </c>
-      <c r="E82" s="36" t="s">
+      <c r="E83" s="55" t="s">
+        <v>352</v>
+      </c>
+      <c r="F83" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G83" s="55" t="s">
         <v>353</v>
       </c>
-      <c r="F82" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="G82" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="H82" s="36" t="s">
-        <v>352</v>
-      </c>
-      <c r="I82" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="J82" s="36">
+      <c r="H83" s="55" t="s">
+        <v>351</v>
+      </c>
+      <c r="I83" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="J83" s="55">
         <v>1</v>
       </c>
-      <c r="K82" s="36">
+      <c r="K83" s="55">
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L82" s="36"/>
-    </row>
-    <row r="83" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="61">
+      <c r="L83" s="55"/>
+    </row>
+    <row r="84" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="56">
         <f t="shared" si="31"/>
-        <v>74</v>
-      </c>
-      <c r="C83" s="66" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" s="61" t="s">
+        <v>347</v>
+      </c>
+      <c r="D84" s="62" t="s">
         <v>348</v>
       </c>
-      <c r="D83" s="67" t="s">
-        <v>349</v>
-      </c>
-      <c r="E83" s="64" t="s">
+      <c r="E84" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="F84" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="G84" s="59" t="s">
         <v>355</v>
       </c>
-      <c r="F83" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="G83" s="64" t="s">
-        <v>356</v>
-      </c>
-      <c r="H83" s="64" t="s">
-        <v>352</v>
-      </c>
-      <c r="I83" s="64" t="s">
-        <v>336</v>
-      </c>
-      <c r="J83" s="64">
+      <c r="H84" s="59" t="s">
+        <v>351</v>
+      </c>
+      <c r="I84" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="J84" s="59">
         <v>1</v>
       </c>
-      <c r="K83" s="64">
+      <c r="K84" s="59">
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L83" s="64"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="43"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="33"/>
-      <c r="F84" s="34"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="34"/>
-      <c r="I84" s="35"/>
-      <c r="J84" s="35"/>
-      <c r="K84" s="35"/>
-      <c r="L84" s="68"/>
-    </row>
-    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="24"/>
-      <c r="C85" s="44"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9"/>
-      <c r="L85" s="65"/>
+      <c r="L84" s="59"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="33"/>
+      <c r="F85" s="34"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="34"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="63"/>
+    </row>
+    <row r="86" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="24"/>
+      <c r="C86" s="43"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
